--- a/research/traditional_assets/database/data/norway/norway_environmental_waste_services.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_environmental_waste_services.xlsx
@@ -1638,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1775,22 +1775,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08062411637343692</v>
+        <v>0.08048184331741536</v>
       </c>
       <c r="C2">
-        <v>564.8006441872652</v>
+        <v>560.8327014219544</v>
       </c>
       <c r="D2">
-        <v>534.6006441872652</v>
+        <v>536.7937014219543</v>
       </c>
       <c r="E2">
-        <v>-181.9</v>
+        <v>-175.739</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.161</v>
       </c>
       <c r="G2">
         <v>30.2</v>
@@ -1811,28 +1811,28 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3098983</v>
       </c>
       <c r="N2">
-        <v>6.79999999999999</v>
+        <v>6.49010169999999</v>
       </c>
       <c r="O2">
-        <v>1.495999999999998</v>
+        <v>1.427822373999998</v>
       </c>
       <c r="P2">
-        <v>5.303999999999992</v>
+        <v>5.062279325999992</v>
       </c>
       <c r="Q2">
-        <v>41.504</v>
+        <v>41.262279326</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08062411637343692</v>
+        <v>0.08089848819940945</v>
       </c>
       <c r="T2">
-        <v>0.8042521102410373</v>
+        <v>0.8105886420186939</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>21.94268248648021</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1857,22 +1857,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08048184331741536</v>
+        <v>0.0803629702613938</v>
       </c>
       <c r="C3">
-        <v>560.8327014219544</v>
+        <v>556.517905821014</v>
       </c>
       <c r="D3">
-        <v>536.7937014219543</v>
+        <v>538.6399058210139</v>
       </c>
       <c r="E3">
-        <v>-175.739</v>
+        <v>-169.578</v>
       </c>
       <c r="F3">
-        <v>6.161</v>
+        <v>12.322</v>
       </c>
       <c r="G3">
         <v>30.2</v>
@@ -1893,45 +1893,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M3">
-        <v>0.3098983</v>
+        <v>0.6382796000000001</v>
       </c>
       <c r="N3">
-        <v>6.49010169999999</v>
+        <v>6.16172039999999</v>
       </c>
       <c r="O3">
-        <v>1.427822373999998</v>
+        <v>1.355578487999998</v>
       </c>
       <c r="P3">
-        <v>5.062279325999992</v>
+        <v>4.806141911999992</v>
       </c>
       <c r="Q3">
-        <v>41.262279326</v>
+        <v>41.006141912</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08089848819940945</v>
+        <v>0.08117845945040184</v>
       </c>
       <c r="T3">
-        <v>0.8105886420186939</v>
+        <v>0.8170544907714048</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>21.94268248648021</v>
+        <v>10.65363831148605</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1939,22 +1939,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0803629702613938</v>
+        <v>0.08029089720537223</v>
       </c>
       <c r="C4">
-        <v>556.517905821014</v>
+        <v>551.4824614676686</v>
       </c>
       <c r="D4">
-        <v>538.6399058210139</v>
+        <v>539.7654614676685</v>
       </c>
       <c r="E4">
-        <v>-169.578</v>
+        <v>-163.417</v>
       </c>
       <c r="F4">
-        <v>12.322</v>
+        <v>18.483</v>
       </c>
       <c r="G4">
         <v>30.2</v>
@@ -1975,45 +1975,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M4">
-        <v>0.6382796000000001</v>
+        <v>1.0036269</v>
       </c>
       <c r="N4">
-        <v>6.16172039999999</v>
+        <v>5.79637309999999</v>
       </c>
       <c r="O4">
-        <v>1.355578487999998</v>
+        <v>1.275202081999998</v>
       </c>
       <c r="P4">
-        <v>4.806141911999992</v>
+        <v>4.521171017999992</v>
       </c>
       <c r="Q4">
-        <v>41.006141912</v>
+        <v>40.72117101799999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08117845945040184</v>
+        <v>0.08146420330450746</v>
       </c>
       <c r="T4">
-        <v>0.8170544907714048</v>
+        <v>0.8236536559932437</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.040404</v>
+        <v>0.042354</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>10.65363831148605</v>
+        <v>6.775426206690942</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2021,22 +2021,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08029089720537223</v>
+        <v>0.08021102414935065</v>
       </c>
       <c r="C5">
-        <v>551.4824614676686</v>
+        <v>546.5743366147495</v>
       </c>
       <c r="D5">
-        <v>539.7654614676685</v>
+        <v>541.0183366147495</v>
       </c>
       <c r="E5">
-        <v>-163.417</v>
+        <v>-157.256</v>
       </c>
       <c r="F5">
-        <v>18.483</v>
+        <v>24.644</v>
       </c>
       <c r="G5">
         <v>30.2</v>
@@ -2057,45 +2057,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M5">
-        <v>1.0036269</v>
+        <v>1.3628132</v>
       </c>
       <c r="N5">
-        <v>5.79637309999999</v>
+        <v>5.43718679999999</v>
       </c>
       <c r="O5">
-        <v>1.275202081999998</v>
+        <v>1.196181095999998</v>
       </c>
       <c r="P5">
-        <v>4.521171017999992</v>
+        <v>4.241005703999992</v>
       </c>
       <c r="Q5">
-        <v>40.72117101799999</v>
+        <v>40.44100570399999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08146420330450746</v>
+        <v>0.0817559001555736</v>
       </c>
       <c r="T5">
-        <v>0.8236536559932437</v>
+        <v>0.8303903038238709</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>6.775426206690942</v>
+        <v>4.989678702847895</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2103,22 +2103,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08021102414935065</v>
+        <v>0.0803417510933291</v>
       </c>
       <c r="C6">
-        <v>546.5743366147495</v>
+        <v>538.365794971859</v>
       </c>
       <c r="D6">
-        <v>541.0183366147495</v>
+        <v>538.9707949718589</v>
       </c>
       <c r="E6">
-        <v>-157.256</v>
+        <v>-151.095</v>
       </c>
       <c r="F6">
-        <v>24.644</v>
+        <v>30.805</v>
       </c>
       <c r="G6">
         <v>30.2</v>
@@ -2139,45 +2139,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M6">
-        <v>1.3628132</v>
+        <v>1.8883465</v>
       </c>
       <c r="N6">
-        <v>5.43718679999999</v>
+        <v>4.91165349999999</v>
       </c>
       <c r="O6">
-        <v>1.196181095999998</v>
+        <v>1.080563769999998</v>
       </c>
       <c r="P6">
-        <v>4.241005703999992</v>
+        <v>3.831089729999992</v>
       </c>
       <c r="Q6">
-        <v>40.44100570399999</v>
+        <v>40.03108973</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0817559001555736</v>
+        <v>0.08205373799297801</v>
       </c>
       <c r="T6">
-        <v>0.8303903038238709</v>
+        <v>0.8372687758193536</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04313400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.989678702847895</v>
+        <v>3.601034026329379</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0803417510933291</v>
+        <v>0.08078135803730754</v>
       </c>
       <c r="C7">
-        <v>538.365794971859</v>
+        <v>525.4316072694684</v>
       </c>
       <c r="D7">
-        <v>538.9707949718589</v>
+        <v>532.1976072694683</v>
       </c>
       <c r="E7">
-        <v>-151.095</v>
+        <v>-144.934</v>
       </c>
       <c r="F7">
-        <v>30.805</v>
+        <v>36.966</v>
       </c>
       <c r="G7">
         <v>30.2</v>
@@ -2221,45 +2221,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M7">
-        <v>1.8883465</v>
+        <v>2.6578554</v>
       </c>
       <c r="N7">
-        <v>4.91165349999999</v>
+        <v>4.142144599999989</v>
       </c>
       <c r="O7">
-        <v>1.080563769999998</v>
+        <v>0.9112718119999976</v>
       </c>
       <c r="P7">
-        <v>3.831089729999992</v>
+        <v>3.230872787999992</v>
       </c>
       <c r="Q7">
-        <v>40.03108973</v>
+        <v>39.43087278799999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08205373799297801</v>
+        <v>0.08235791280564632</v>
       </c>
       <c r="T7">
-        <v>0.8372687758193536</v>
+        <v>0.844293598282825</v>
       </c>
       <c r="U7">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.047814</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.601034026329379</v>
+        <v>2.558453706699013</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2267,22 +2267,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08078135803730754</v>
+        <v>0.08102050498128598</v>
       </c>
       <c r="C8">
-        <v>525.4316072694684</v>
+        <v>515.6569898202367</v>
       </c>
       <c r="D8">
-        <v>532.1976072694683</v>
+        <v>528.5839898202366</v>
       </c>
       <c r="E8">
-        <v>-144.934</v>
+        <v>-138.773</v>
       </c>
       <c r="F8">
-        <v>36.966</v>
+        <v>43.127</v>
       </c>
       <c r="G8">
         <v>30.2</v>
@@ -2303,45 +2303,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M8">
-        <v>2.6578554</v>
+        <v>3.2690266</v>
       </c>
       <c r="N8">
-        <v>4.142144599999989</v>
+        <v>3.53097339999999</v>
       </c>
       <c r="O8">
-        <v>0.9112718119999976</v>
+        <v>0.7768141479999978</v>
       </c>
       <c r="P8">
-        <v>3.230872787999992</v>
+        <v>2.754159251999992</v>
       </c>
       <c r="Q8">
-        <v>39.43087278799999</v>
+        <v>38.954159252</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08235791280564632</v>
+        <v>0.08266862901213545</v>
       </c>
       <c r="T8">
-        <v>0.844293598282825</v>
+        <v>0.8514694921971239</v>
       </c>
       <c r="U8">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.558453706699013</v>
+        <v>2.080129907783555</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2349,22 +2349,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.081020504981286</v>
+        <v>0.08196321192526443</v>
       </c>
       <c r="C9">
-        <v>515.6569898202364</v>
+        <v>495.7167990030833</v>
       </c>
       <c r="D9">
-        <v>528.5839898202363</v>
+        <v>514.8047990030833</v>
       </c>
       <c r="E9">
-        <v>-138.773</v>
+        <v>-132.612</v>
       </c>
       <c r="F9">
-        <v>43.127</v>
+        <v>49.288</v>
       </c>
       <c r="G9">
         <v>30.2</v>
@@ -2385,45 +2385,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M9">
-        <v>3.269026600000001</v>
+        <v>4.43592</v>
       </c>
       <c r="N9">
-        <v>3.530973399999989</v>
+        <v>2.36407999999999</v>
       </c>
       <c r="O9">
-        <v>0.7768141479999977</v>
+        <v>0.5200975999999977</v>
       </c>
       <c r="P9">
-        <v>2.754159251999992</v>
+        <v>1.843982399999992</v>
       </c>
       <c r="Q9">
-        <v>38.954159252</v>
+        <v>38.0439824</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08266862901213548</v>
+        <v>0.08298609991876568</v>
       </c>
       <c r="T9">
-        <v>0.8514694921971241</v>
+        <v>0.858801383805212</v>
       </c>
       <c r="U9">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.080129907783555</v>
+        <v>1.532940179263826</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2431,22 +2431,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08196321192526443</v>
+        <v>0.08670992327853763</v>
       </c>
       <c r="C10">
-        <v>495.7167990030833</v>
+        <v>429.8238418564061</v>
       </c>
       <c r="D10">
-        <v>514.8047990030833</v>
+        <v>455.0728418564061</v>
       </c>
       <c r="E10">
-        <v>-132.612</v>
+        <v>-126.451</v>
       </c>
       <c r="F10">
-        <v>49.288</v>
+        <v>55.449</v>
       </c>
       <c r="G10">
         <v>30.2</v>
@@ -2467,45 +2467,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M10">
-        <v>4.43592</v>
+        <v>8.139913200000001</v>
       </c>
       <c r="N10">
-        <v>2.36407999999999</v>
+        <v>-1.33991320000001</v>
       </c>
       <c r="O10">
-        <v>0.5200975999999977</v>
+        <v>-0.2947809040000023</v>
       </c>
       <c r="P10">
-        <v>1.843982399999992</v>
+        <v>-1.045132296000008</v>
       </c>
       <c r="Q10">
-        <v>38.0439824</v>
+        <v>35.154867704</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08298609991876568</v>
+        <v>0.08343527529944124</v>
       </c>
       <c r="T10">
-        <v>0.858801383805212</v>
+        <v>0.8691749491787816</v>
       </c>
       <c r="U10">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V10">
-        <v>0.22</v>
+        <v>0.1837857435629655</v>
       </c>
       <c r="W10">
-        <v>0.0702</v>
+        <v>0.1198202528449567</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y10">
-        <v>1.532940179263826</v>
+        <v>0.8353897434680249</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2513,22 +2513,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08670992327853763</v>
+        <v>0.09327482793964845</v>
       </c>
       <c r="C11">
-        <v>429.8238418564061</v>
+        <v>360.7345501636824</v>
       </c>
       <c r="D11">
-        <v>455.0728418564061</v>
+        <v>392.1445501636824</v>
       </c>
       <c r="E11">
-        <v>-126.451</v>
+        <v>-120.29</v>
       </c>
       <c r="F11">
-        <v>55.449</v>
+        <v>61.61</v>
       </c>
       <c r="G11">
         <v>30.2</v>
@@ -2549,45 +2549,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M11">
-        <v>8.139913200000001</v>
+        <v>12.371288</v>
       </c>
       <c r="N11">
-        <v>-1.33991320000001</v>
+        <v>-5.57128800000001</v>
       </c>
       <c r="O11">
-        <v>-0.2947809040000023</v>
+        <v>-1.225683360000002</v>
       </c>
       <c r="P11">
-        <v>-1.045132296000008</v>
+        <v>-4.345604640000007</v>
       </c>
       <c r="Q11">
-        <v>35.154867704</v>
+        <v>31.85439535999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08343527529944124</v>
+        <v>0.08402556131511371</v>
       </c>
       <c r="T11">
-        <v>0.8691749491787816</v>
+        <v>0.8828074206723722</v>
       </c>
       <c r="U11">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.1837857435629655</v>
+        <v>0.120925161551489</v>
       </c>
       <c r="W11">
-        <v>0.1198202528449567</v>
+        <v>0.176518227560461</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.8353897434680249</v>
+        <v>0.5496598252340411</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2595,22 +2595,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09327482793964845</v>
+        <v>0.09873733384144746</v>
       </c>
       <c r="C12">
-        <v>360.7345501636824</v>
+        <v>314.1088768568775</v>
       </c>
       <c r="D12">
-        <v>392.1445501636824</v>
+        <v>351.6798768568776</v>
       </c>
       <c r="E12">
-        <v>-120.29</v>
+        <v>-114.129</v>
       </c>
       <c r="F12">
-        <v>61.61000000000001</v>
+        <v>67.771</v>
       </c>
       <c r="G12">
         <v>30.2</v>
@@ -2631,45 +2631,45 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M12">
-        <v>12.371288</v>
+        <v>15.9804018</v>
       </c>
       <c r="N12">
-        <v>-5.571288000000012</v>
+        <v>-9.180401800000011</v>
       </c>
       <c r="O12">
-        <v>-1.225683360000003</v>
+        <v>-2.019688396000002</v>
       </c>
       <c r="P12">
-        <v>-4.345604640000009</v>
+        <v>-7.160713404000008</v>
       </c>
       <c r="Q12">
-        <v>31.85439535999999</v>
+        <v>29.039286596</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08402556131511371</v>
+        <v>0.08452529335438355</v>
       </c>
       <c r="T12">
-        <v>0.8828074206723722</v>
+        <v>0.8943485763137081</v>
       </c>
       <c r="U12">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.120925161551489</v>
+        <v>0.09361466743595882</v>
       </c>
       <c r="W12">
-        <v>0.176518227560461</v>
+        <v>0.2137256614186009</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y12">
-        <v>0.549659825234041</v>
+        <v>0.4255212156179946</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2677,22 +2677,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09873733384144746</v>
+        <v>0.1006373338414475</v>
       </c>
       <c r="C13">
-        <v>314.1088768568775</v>
+        <v>295.762897770184</v>
       </c>
       <c r="D13">
-        <v>351.6798768568776</v>
+        <v>339.494897770184</v>
       </c>
       <c r="E13">
-        <v>-114.129</v>
+        <v>-107.968</v>
       </c>
       <c r="F13">
-        <v>67.771</v>
+        <v>73.932</v>
       </c>
       <c r="G13">
         <v>30.2</v>
@@ -2713,37 +2713,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M13">
-        <v>15.9804018</v>
+        <v>17.4331656</v>
       </c>
       <c r="N13">
-        <v>-9.180401800000011</v>
+        <v>-10.63316560000001</v>
       </c>
       <c r="O13">
-        <v>-2.019688396000002</v>
+        <v>-2.339296432000003</v>
       </c>
       <c r="P13">
-        <v>-7.160713404000008</v>
+        <v>-8.293869168000009</v>
       </c>
       <c r="Q13">
-        <v>29.039286596</v>
+        <v>27.906130832</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08452529335438355</v>
+        <v>0.08496535350613792</v>
       </c>
       <c r="T13">
-        <v>0.8943485763137081</v>
+        <v>0.9045116283172729</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.09361466743595882</v>
+        <v>0.08581344514962891</v>
       </c>
       <c r="W13">
-        <v>0.2137256614186009</v>
+        <v>0.2155651896337175</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.4255212156179946</v>
+        <v>0.390061114316495</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2759,22 +2759,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1006373338414475</v>
+        <v>0.1025373338414475</v>
       </c>
       <c r="C14">
-        <v>295.762897770184</v>
+        <v>278.2330113229301</v>
       </c>
       <c r="D14">
-        <v>339.494897770184</v>
+        <v>328.1260113229301</v>
       </c>
       <c r="E14">
-        <v>-107.968</v>
+        <v>-101.807</v>
       </c>
       <c r="F14">
-        <v>73.932</v>
+        <v>80.093</v>
       </c>
       <c r="G14">
         <v>30.2</v>
@@ -2795,37 +2795,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M14">
-        <v>17.4331656</v>
+        <v>18.8859294</v>
       </c>
       <c r="N14">
-        <v>-10.63316560000001</v>
+        <v>-12.08592940000001</v>
       </c>
       <c r="O14">
-        <v>-2.339296432000003</v>
+        <v>-2.658904468000002</v>
       </c>
       <c r="P14">
-        <v>-8.293869168000009</v>
+        <v>-9.427024932000009</v>
       </c>
       <c r="Q14">
-        <v>27.906130832</v>
+        <v>26.77297506799999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08496535350613792</v>
+        <v>0.08541552998321997</v>
       </c>
       <c r="T14">
-        <v>0.9045116283172729</v>
+        <v>0.9149083137002302</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.08581344514962891</v>
+        <v>0.07921241090734976</v>
       </c>
       <c r="W14">
-        <v>0.2155651896337175</v>
+        <v>0.2171217135080469</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.390061114316495</v>
+        <v>0.3600564132152262</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2841,22 +2841,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1025373338414475</v>
+        <v>0.1044373338414475</v>
       </c>
       <c r="C15">
-        <v>278.2330113229301</v>
+        <v>261.4398870316158</v>
       </c>
       <c r="D15">
-        <v>328.1260113229301</v>
+        <v>317.4938870316158</v>
       </c>
       <c r="E15">
-        <v>-101.807</v>
+        <v>-95.646</v>
       </c>
       <c r="F15">
-        <v>80.093</v>
+        <v>86.254</v>
       </c>
       <c r="G15">
         <v>30.2</v>
@@ -2877,37 +2877,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M15">
-        <v>18.8859294</v>
+        <v>20.3386932</v>
       </c>
       <c r="N15">
-        <v>-12.08592940000001</v>
+        <v>-13.53869320000001</v>
       </c>
       <c r="O15">
-        <v>-2.658904468000002</v>
+        <v>-2.978512504000002</v>
       </c>
       <c r="P15">
-        <v>-9.427024932000009</v>
+        <v>-10.56018069600001</v>
       </c>
       <c r="Q15">
-        <v>26.77297506799999</v>
+        <v>25.63981930399999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08541552998321997</v>
+        <v>0.08587617568069926</v>
       </c>
       <c r="T15">
-        <v>0.9149083137002302</v>
+        <v>0.9255467824641862</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.07921241090734976</v>
+        <v>0.07355438155682478</v>
       </c>
       <c r="W15">
-        <v>0.2171217135080469</v>
+        <v>0.2184558768289007</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3600564132152262</v>
+        <v>0.3343380979855672</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2923,22 +2923,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1044373338414475</v>
+        <v>0.1063373338414475</v>
       </c>
       <c r="C16">
-        <v>261.4398870316158</v>
+        <v>245.3141537491753</v>
       </c>
       <c r="D16">
-        <v>317.4938870316158</v>
+        <v>307.5291537491754</v>
       </c>
       <c r="E16">
-        <v>-95.646</v>
+        <v>-89.48499999999999</v>
       </c>
       <c r="F16">
-        <v>86.254</v>
+        <v>92.41500000000002</v>
       </c>
       <c r="G16">
         <v>30.2</v>
@@ -2959,37 +2959,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M16">
-        <v>20.3386932</v>
+        <v>21.791457</v>
       </c>
       <c r="N16">
-        <v>-13.53869320000001</v>
+        <v>-14.99145700000001</v>
       </c>
       <c r="O16">
-        <v>-2.978512504000002</v>
+        <v>-3.298120540000003</v>
       </c>
       <c r="P16">
-        <v>-10.56018069600001</v>
+        <v>-11.69333646000001</v>
       </c>
       <c r="Q16">
-        <v>25.63981930399999</v>
+        <v>24.50666353999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08587617568069926</v>
+        <v>0.08634766010047221</v>
       </c>
       <c r="T16">
-        <v>0.9255467824641862</v>
+        <v>0.9364355681402355</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.07355438155682478</v>
+        <v>0.06865075611970313</v>
       </c>
       <c r="W16">
-        <v>0.2184558768289007</v>
+        <v>0.219612151706974</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3343380979855672</v>
+        <v>0.312048891453196</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3005,22 +3005,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1063373338414475</v>
+        <v>0.1082373338414475</v>
       </c>
       <c r="C17">
-        <v>245.3141537491754</v>
+        <v>229.7948843264738</v>
       </c>
       <c r="D17">
-        <v>307.5291537491755</v>
+        <v>298.1708843264738</v>
       </c>
       <c r="E17">
-        <v>-89.485</v>
+        <v>-83.324</v>
       </c>
       <c r="F17">
-        <v>92.41500000000001</v>
+        <v>98.57600000000001</v>
       </c>
       <c r="G17">
         <v>30.2</v>
@@ -3041,37 +3041,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M17">
-        <v>21.791457</v>
+        <v>23.2442208</v>
       </c>
       <c r="N17">
-        <v>-14.99145700000001</v>
+        <v>-16.44422080000001</v>
       </c>
       <c r="O17">
-        <v>-3.298120540000002</v>
+        <v>-3.617728576000003</v>
       </c>
       <c r="P17">
-        <v>-11.69333646000001</v>
+        <v>-12.82649222400001</v>
       </c>
       <c r="Q17">
-        <v>24.50666353999999</v>
+        <v>23.37350777599999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08634766010047221</v>
+        <v>0.08683037033976353</v>
       </c>
       <c r="T17">
-        <v>0.9364355681402355</v>
+        <v>0.9475836106180954</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.06865075611970314</v>
+        <v>0.06436008386222168</v>
       </c>
       <c r="W17">
-        <v>0.219612151706974</v>
+        <v>0.2206238922252881</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.312048891453196</v>
+        <v>0.2925458357373713</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3087,22 +3087,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1082373338414475</v>
+        <v>0.1101373338414475</v>
       </c>
       <c r="C18">
-        <v>229.7948843264738</v>
+        <v>214.8283487782267</v>
       </c>
       <c r="D18">
-        <v>298.1708843264738</v>
+        <v>289.3653487782267</v>
       </c>
       <c r="E18">
-        <v>-83.324</v>
+        <v>-77.163</v>
       </c>
       <c r="F18">
-        <v>98.57600000000001</v>
+        <v>104.737</v>
       </c>
       <c r="G18">
         <v>30.2</v>
@@ -3123,37 +3123,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M18">
-        <v>23.2442208</v>
+        <v>24.6969846</v>
       </c>
       <c r="N18">
-        <v>-16.44422080000001</v>
+        <v>-17.89698460000001</v>
       </c>
       <c r="O18">
-        <v>-3.617728576000003</v>
+        <v>-3.937336612000003</v>
       </c>
       <c r="P18">
-        <v>-12.82649222400001</v>
+        <v>-13.95964798800001</v>
       </c>
       <c r="Q18">
-        <v>23.37350777599999</v>
+        <v>22.24035201199999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08683037033976353</v>
+        <v>0.08732471215108598</v>
       </c>
       <c r="T18">
-        <v>0.9475836106180954</v>
+        <v>0.9590002806255423</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.06436008386222168</v>
+        <v>0.06057419657620864</v>
       </c>
       <c r="W18">
-        <v>0.2206238922252881</v>
+        <v>0.22151660444733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2925458357373713</v>
+        <v>0.2753372571645848</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1101373338414475</v>
+        <v>0.1120373338414475</v>
       </c>
       <c r="C19">
-        <v>214.8283487782267</v>
+        <v>200.366982039513</v>
       </c>
       <c r="D19">
-        <v>289.3653487782267</v>
+        <v>281.064982039513</v>
       </c>
       <c r="E19">
-        <v>-77.163</v>
+        <v>-71.002</v>
       </c>
       <c r="F19">
-        <v>104.737</v>
+        <v>110.898</v>
       </c>
       <c r="G19">
         <v>30.2</v>
@@ -3205,37 +3205,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M19">
-        <v>24.6969846</v>
+        <v>26.1497484</v>
       </c>
       <c r="N19">
-        <v>-17.89698460000001</v>
+        <v>-19.34974840000001</v>
       </c>
       <c r="O19">
-        <v>-3.937336612000003</v>
+        <v>-4.256944648000003</v>
       </c>
       <c r="P19">
-        <v>-13.95964798800001</v>
+        <v>-15.09280375200001</v>
       </c>
       <c r="Q19">
-        <v>22.24035201199999</v>
+        <v>21.10719624799999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08732471215108598</v>
+        <v>0.08783111107975776</v>
       </c>
       <c r="T19">
-        <v>0.9590002806255423</v>
+        <v>0.9706954059990245</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.06057419657620864</v>
+        <v>0.05720896343308594</v>
       </c>
       <c r="W19">
-        <v>0.22151660444733</v>
+        <v>0.2223101264224784</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2753372571645848</v>
+        <v>0.2600407428776633</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1120373338414475</v>
+        <v>0.1139373338414475</v>
       </c>
       <c r="C20">
-        <v>200.366982039513</v>
+        <v>186.3685244260741</v>
       </c>
       <c r="D20">
-        <v>281.064982039513</v>
+        <v>273.2275244260742</v>
       </c>
       <c r="E20">
-        <v>-71.00200000000001</v>
+        <v>-64.84099999999999</v>
       </c>
       <c r="F20">
-        <v>110.898</v>
+        <v>117.059</v>
       </c>
       <c r="G20">
         <v>30.2</v>
@@ -3287,37 +3287,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M20">
-        <v>26.1497484</v>
+        <v>27.6025122</v>
       </c>
       <c r="N20">
-        <v>-19.34974840000001</v>
+        <v>-20.80251220000001</v>
       </c>
       <c r="O20">
-        <v>-4.256944648000002</v>
+        <v>-4.576552684000003</v>
       </c>
       <c r="P20">
-        <v>-15.09280375200001</v>
+        <v>-16.22595951600001</v>
       </c>
       <c r="Q20">
-        <v>21.10719624799999</v>
+        <v>19.97404048399999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08783111107975776</v>
+        <v>0.0883500136856807</v>
       </c>
       <c r="T20">
-        <v>0.9706954059990245</v>
+        <v>0.982679299900247</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05720896343308596</v>
+        <v>0.05419796535766037</v>
       </c>
       <c r="W20">
-        <v>0.2223101264224784</v>
+        <v>0.2230201197686637</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2600407428776634</v>
+        <v>0.2463543879893653</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3333,22 +3333,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1139373338414475</v>
+        <v>0.1158373338414475</v>
       </c>
       <c r="C21">
-        <v>186.3685244260741</v>
+        <v>172.795302002177</v>
       </c>
       <c r="D21">
-        <v>273.2275244260742</v>
+        <v>265.8153020021771</v>
       </c>
       <c r="E21">
-        <v>-64.84099999999999</v>
+        <v>-58.67999999999999</v>
       </c>
       <c r="F21">
-        <v>117.059</v>
+        <v>123.22</v>
       </c>
       <c r="G21">
         <v>30.2</v>
@@ -3369,37 +3369,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M21">
-        <v>27.6025122</v>
+        <v>29.055276</v>
       </c>
       <c r="N21">
-        <v>-20.80251220000001</v>
+        <v>-22.25527600000001</v>
       </c>
       <c r="O21">
-        <v>-4.576552684000003</v>
+        <v>-4.896160720000003</v>
       </c>
       <c r="P21">
-        <v>-16.22595951600001</v>
+        <v>-17.35911528000001</v>
       </c>
       <c r="Q21">
-        <v>19.97404048399999</v>
+        <v>18.84088471999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0883500136856807</v>
+        <v>0.08888188885675172</v>
       </c>
       <c r="T21">
-        <v>0.982679299900247</v>
+        <v>0.9949627911490002</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05419796535766037</v>
+        <v>0.05148806708977735</v>
       </c>
       <c r="W21">
-        <v>0.2230201197686637</v>
+        <v>0.2236591137802305</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2463543879893653</v>
+        <v>0.234036668589897</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3415,22 +3415,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1158373338414475</v>
+        <v>0.1177373338414475</v>
       </c>
       <c r="C22">
-        <v>172.795302002177</v>
+        <v>159.6136209894877</v>
       </c>
       <c r="D22">
-        <v>265.8153020021771</v>
+        <v>258.7946209894878</v>
       </c>
       <c r="E22">
-        <v>-58.67999999999999</v>
+        <v>-52.51899999999998</v>
       </c>
       <c r="F22">
-        <v>123.22</v>
+        <v>129.381</v>
       </c>
       <c r="G22">
         <v>30.2</v>
@@ -3451,37 +3451,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M22">
-        <v>29.055276</v>
+        <v>30.50803980000001</v>
       </c>
       <c r="N22">
-        <v>-22.25527600000001</v>
+        <v>-23.70803980000002</v>
       </c>
       <c r="O22">
-        <v>-4.896160720000003</v>
+        <v>-5.215768756000005</v>
       </c>
       <c r="P22">
-        <v>-17.35911528000001</v>
+        <v>-18.49227104400001</v>
       </c>
       <c r="Q22">
-        <v>18.84088471999999</v>
+        <v>17.70772895599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08888188885675172</v>
+        <v>0.08942722922202705</v>
       </c>
       <c r="T22">
-        <v>0.9949627911490002</v>
+        <v>1.007557256859747</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05148806708977735</v>
+        <v>0.04903625437121651</v>
       </c>
       <c r="W22">
-        <v>0.2236591137802305</v>
+        <v>0.2242372512192672</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.234036668589897</v>
+        <v>0.2228920653237114</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3497,22 +3497,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1177373338414475</v>
+        <v>0.1196373338414475</v>
       </c>
       <c r="C23">
-        <v>159.6136209894879</v>
+        <v>146.7932556752433</v>
       </c>
       <c r="D23">
-        <v>258.7946209894879</v>
+        <v>252.1352556752433</v>
       </c>
       <c r="E23">
-        <v>-52.51900000000001</v>
+        <v>-46.358</v>
       </c>
       <c r="F23">
-        <v>129.381</v>
+        <v>135.542</v>
       </c>
       <c r="G23">
         <v>30.2</v>
@@ -3533,37 +3533,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M23">
-        <v>30.5080398</v>
+        <v>31.9608036</v>
       </c>
       <c r="N23">
-        <v>-23.70803980000001</v>
+        <v>-25.16080360000001</v>
       </c>
       <c r="O23">
-        <v>-5.215768756000003</v>
+        <v>-5.535376792000003</v>
       </c>
       <c r="P23">
-        <v>-18.49227104400001</v>
+        <v>-19.62542680800001</v>
       </c>
       <c r="Q23">
-        <v>17.70772895599999</v>
+        <v>16.574573192</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08942722922202705</v>
+        <v>0.0899865526735915</v>
       </c>
       <c r="T23">
-        <v>1.007557256859747</v>
+        <v>1.020474657588718</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.04903625437121652</v>
+        <v>0.04680733371797941</v>
       </c>
       <c r="W23">
-        <v>0.2242372512192672</v>
+        <v>0.2247628307093005</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2228920653237114</v>
+        <v>0.2127606078089973</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3579,22 +3579,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1196373338414475</v>
+        <v>0.1215373338414475</v>
       </c>
       <c r="C24">
-        <v>146.7932556752433</v>
+        <v>134.3070134005966</v>
       </c>
       <c r="D24">
-        <v>252.1352556752433</v>
+        <v>245.8100134005966</v>
       </c>
       <c r="E24">
-        <v>-46.358</v>
+        <v>-40.197</v>
       </c>
       <c r="F24">
-        <v>135.542</v>
+        <v>141.703</v>
       </c>
       <c r="G24">
         <v>30.2</v>
@@ -3615,37 +3615,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M24">
-        <v>31.9608036</v>
+        <v>33.41356740000001</v>
       </c>
       <c r="N24">
-        <v>-25.16080360000001</v>
+        <v>-26.61356740000002</v>
       </c>
       <c r="O24">
-        <v>-5.535376792000003</v>
+        <v>-5.854984828000004</v>
       </c>
       <c r="P24">
-        <v>-19.62542680800001</v>
+        <v>-20.75858257200001</v>
       </c>
       <c r="Q24">
-        <v>16.574573192</v>
+        <v>15.44141742799999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0899865526735915</v>
+        <v>0.09056040400701476</v>
       </c>
       <c r="T24">
-        <v>1.020474657588718</v>
+        <v>1.033727575219741</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04680733371797941</v>
+        <v>0.0447722322519803</v>
       </c>
       <c r="W24">
-        <v>0.2247628307093005</v>
+        <v>0.2252427076349831</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2127606078089973</v>
+        <v>0.2035101465999105</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3661,22 +3661,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1215373338414475</v>
+        <v>0.1234373338414475</v>
       </c>
       <c r="C25">
-        <v>134.3070134005966</v>
+        <v>122.130363424582</v>
       </c>
       <c r="D25">
-        <v>245.8100134005966</v>
+        <v>239.794363424582</v>
       </c>
       <c r="E25">
-        <v>-40.197</v>
+        <v>-34.036</v>
       </c>
       <c r="F25">
-        <v>141.703</v>
+        <v>147.864</v>
       </c>
       <c r="G25">
         <v>30.2</v>
@@ -3697,37 +3697,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M25">
-        <v>33.41356740000001</v>
+        <v>34.8663312</v>
       </c>
       <c r="N25">
-        <v>-26.61356740000002</v>
+        <v>-28.06633120000001</v>
       </c>
       <c r="O25">
-        <v>-5.854984828000004</v>
+        <v>-6.174592864000004</v>
       </c>
       <c r="P25">
-        <v>-20.75858257200001</v>
+        <v>-21.89173833600001</v>
       </c>
       <c r="Q25">
-        <v>15.44141742799999</v>
+        <v>14.30826166399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09056040400701476</v>
+        <v>0.09114935669131759</v>
       </c>
       <c r="T25">
-        <v>1.033727575219741</v>
+        <v>1.047329253841053</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.0447722322519803</v>
+        <v>0.04290672257481445</v>
       </c>
       <c r="W25">
-        <v>0.2252427076349831</v>
+        <v>0.2256825948168588</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2035101465999105</v>
+        <v>0.1950305571582476</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3743,22 +3743,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1234373338414475</v>
+        <v>0.1253373338414475</v>
       </c>
       <c r="C26">
-        <v>122.1303634245822</v>
+        <v>110.241118982608</v>
       </c>
       <c r="D26">
-        <v>239.7943634245822</v>
+        <v>234.0661189826079</v>
       </c>
       <c r="E26">
-        <v>-34.036</v>
+        <v>-27.875</v>
       </c>
       <c r="F26">
-        <v>147.864</v>
+        <v>154.025</v>
       </c>
       <c r="G26">
         <v>30.2</v>
@@ -3779,37 +3779,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M26">
-        <v>34.8663312</v>
+        <v>36.319095</v>
       </c>
       <c r="N26">
-        <v>-28.06633120000001</v>
+        <v>-29.51909500000001</v>
       </c>
       <c r="O26">
-        <v>-6.174592864000004</v>
+        <v>-6.494200900000004</v>
       </c>
       <c r="P26">
-        <v>-21.89173833600001</v>
+        <v>-23.02489410000001</v>
       </c>
       <c r="Q26">
-        <v>14.30826166399999</v>
+        <v>13.17510589999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09114935669131759</v>
+        <v>0.09175401478053516</v>
       </c>
       <c r="T26">
-        <v>1.047329253841053</v>
+        <v>1.061293643892267</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04290672257481445</v>
+        <v>0.04119045367182188</v>
       </c>
       <c r="W26">
-        <v>0.2256825948168588</v>
+        <v>0.2260872910241844</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1950305571582476</v>
+        <v>0.1872293348719176</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3825,22 +3825,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1253373338414475</v>
+        <v>0.1272373338414475</v>
       </c>
       <c r="C27">
-        <v>110.241118982608</v>
+        <v>98.61916385196966</v>
       </c>
       <c r="D27">
-        <v>234.0661189826079</v>
+        <v>228.6051638519697</v>
       </c>
       <c r="E27">
-        <v>-27.875</v>
+        <v>-21.714</v>
       </c>
       <c r="F27">
-        <v>154.025</v>
+        <v>160.186</v>
       </c>
       <c r="G27">
         <v>30.2</v>
@@ -3861,37 +3861,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M27">
-        <v>36.319095</v>
+        <v>37.7718588</v>
       </c>
       <c r="N27">
-        <v>-29.51909500000001</v>
+        <v>-30.97185880000001</v>
       </c>
       <c r="O27">
-        <v>-6.494200900000004</v>
+        <v>-6.813808936000003</v>
       </c>
       <c r="P27">
-        <v>-23.02489410000001</v>
+        <v>-24.15804986400001</v>
       </c>
       <c r="Q27">
-        <v>13.17510589999999</v>
+        <v>12.04195013599999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09175401478053516</v>
+        <v>0.09237501498027212</v>
       </c>
       <c r="T27">
-        <v>1.061293643892267</v>
+        <v>1.075635449890811</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04119045367182188</v>
+        <v>0.03960620545367488</v>
       </c>
       <c r="W27">
-        <v>0.2260872910241844</v>
+        <v>0.2264608567540235</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1872293348719176</v>
+        <v>0.1800282066076131</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3907,22 +3907,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1272373338414475</v>
+        <v>0.1291373338414475</v>
       </c>
       <c r="C28">
-        <v>98.61916385196966</v>
+        <v>87.24621632140551</v>
       </c>
       <c r="D28">
-        <v>228.6051638519697</v>
+        <v>223.3932163214055</v>
       </c>
       <c r="E28">
-        <v>-21.714</v>
+        <v>-15.553</v>
       </c>
       <c r="F28">
-        <v>160.186</v>
+        <v>166.347</v>
       </c>
       <c r="G28">
         <v>30.2</v>
@@ -3943,37 +3943,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M28">
-        <v>37.7718588</v>
+        <v>39.2246226</v>
       </c>
       <c r="N28">
-        <v>-30.97185880000001</v>
+        <v>-32.42462260000001</v>
       </c>
       <c r="O28">
-        <v>-6.813808936000003</v>
+        <v>-7.133416972000003</v>
       </c>
       <c r="P28">
-        <v>-24.15804986400001</v>
+        <v>-25.29120562800001</v>
       </c>
       <c r="Q28">
-        <v>12.04195013599999</v>
+        <v>10.90879437199999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09237501498027212</v>
+        <v>0.09301302888411145</v>
       </c>
       <c r="T28">
-        <v>1.075635449890811</v>
+        <v>1.090370182081096</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.03960620545367488</v>
+        <v>0.03813930895539062</v>
       </c>
       <c r="W28">
-        <v>0.2264608567540235</v>
+        <v>0.2268067509483189</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1800282066076131</v>
+        <v>0.1733604952517755</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3989,22 +3989,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1291373338414475</v>
+        <v>0.1310373338414475</v>
       </c>
       <c r="C29">
-        <v>87.24621632140551</v>
+        <v>76.10562472835767</v>
       </c>
       <c r="D29">
-        <v>223.3932163214055</v>
+        <v>218.4136247283577</v>
       </c>
       <c r="E29">
-        <v>-15.553</v>
+        <v>-9.391999999999996</v>
       </c>
       <c r="F29">
-        <v>166.347</v>
+        <v>172.508</v>
       </c>
       <c r="G29">
         <v>30.2</v>
@@ -4025,37 +4025,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M29">
-        <v>39.2246226</v>
+        <v>40.6773864</v>
       </c>
       <c r="N29">
-        <v>-32.42462260000001</v>
+        <v>-33.87738640000001</v>
       </c>
       <c r="O29">
-        <v>-7.133416972000003</v>
+        <v>-7.453025008000003</v>
       </c>
       <c r="P29">
-        <v>-25.29120562800001</v>
+        <v>-26.42436139200001</v>
       </c>
       <c r="Q29">
-        <v>10.90879437199999</v>
+        <v>9.775638607999994</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09301302888411145</v>
+        <v>0.0936687653963908</v>
       </c>
       <c r="T29">
-        <v>1.090370182081096</v>
+        <v>1.105514212387778</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03813930895539062</v>
+        <v>0.03677719077841239</v>
       </c>
       <c r="W29">
-        <v>0.2268067509483189</v>
+        <v>0.2271279384144504</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1733604952517755</v>
+        <v>0.1671690489927836</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4071,22 +4071,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1310373338414475</v>
+        <v>0.1329373338414475</v>
       </c>
       <c r="C30">
-        <v>76.10562472835767</v>
+        <v>65.18218974567887</v>
       </c>
       <c r="D30">
-        <v>218.4136247283577</v>
+        <v>213.6511897456789</v>
       </c>
       <c r="E30">
-        <v>-9.391999999999996</v>
+        <v>-3.230999999999966</v>
       </c>
       <c r="F30">
-        <v>172.508</v>
+        <v>178.669</v>
       </c>
       <c r="G30">
         <v>30.2</v>
@@ -4107,37 +4107,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M30">
-        <v>40.6773864</v>
+        <v>42.13015020000001</v>
       </c>
       <c r="N30">
-        <v>-33.87738640000001</v>
+        <v>-35.33015020000002</v>
       </c>
       <c r="O30">
-        <v>-7.453025008000003</v>
+        <v>-7.772633044000004</v>
       </c>
       <c r="P30">
-        <v>-26.42436139200001</v>
+        <v>-27.55751715600002</v>
       </c>
       <c r="Q30">
-        <v>9.775638607999994</v>
+        <v>8.642482843999986</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0936687653963908</v>
+        <v>0.09434297335972024</v>
       </c>
       <c r="T30">
-        <v>1.105514212387778</v>
+        <v>1.121084835097465</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03677719077841239</v>
+        <v>0.03550901178605333</v>
       </c>
       <c r="W30">
-        <v>0.2271279384144504</v>
+        <v>0.2274269750208486</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1671690489927836</v>
+        <v>0.1614045990275151</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4153,22 +4153,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1329373338414475</v>
+        <v>0.1348373338414475</v>
       </c>
       <c r="C31">
-        <v>65.18218974567893</v>
+        <v>54.46200942206696</v>
       </c>
       <c r="D31">
-        <v>213.6511897456789</v>
+        <v>209.092009422067</v>
       </c>
       <c r="E31">
-        <v>-3.231000000000023</v>
+        <v>2.930000000000007</v>
       </c>
       <c r="F31">
-        <v>178.669</v>
+        <v>184.83</v>
       </c>
       <c r="G31">
         <v>30.2</v>
@@ -4189,37 +4189,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M31">
-        <v>42.1301502</v>
+        <v>43.582914</v>
       </c>
       <c r="N31">
-        <v>-35.33015020000001</v>
+        <v>-36.78291400000001</v>
       </c>
       <c r="O31">
-        <v>-7.772633044000001</v>
+        <v>-8.092241080000003</v>
       </c>
       <c r="P31">
-        <v>-27.557517156</v>
+        <v>-28.69067292000001</v>
       </c>
       <c r="Q31">
-        <v>8.642482844</v>
+        <v>7.509327079999991</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09434297335972024</v>
+        <v>0.09503644440771623</v>
       </c>
       <c r="T31">
-        <v>1.121084835097465</v>
+        <v>1.137100332741714</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03550901178605335</v>
+        <v>0.03432537805985157</v>
       </c>
       <c r="W31">
-        <v>0.2274269750208486</v>
+        <v>0.227706075853487</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1614045990275152</v>
+        <v>0.156024445726598</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4235,22 +4235,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1348373338414475</v>
+        <v>0.1367373338414475</v>
       </c>
       <c r="C32">
-        <v>54.46200942206696</v>
+        <v>43.93234364839702</v>
       </c>
       <c r="D32">
-        <v>209.092009422067</v>
+        <v>204.723343648397</v>
       </c>
       <c r="E32">
-        <v>2.930000000000007</v>
+        <v>9.091000000000008</v>
       </c>
       <c r="F32">
-        <v>184.83</v>
+        <v>190.991</v>
       </c>
       <c r="G32">
         <v>30.2</v>
@@ -4271,37 +4271,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M32">
-        <v>43.582914</v>
+        <v>45.0356778</v>
       </c>
       <c r="N32">
-        <v>-36.78291400000001</v>
+        <v>-38.23567780000001</v>
       </c>
       <c r="O32">
-        <v>-8.092241080000003</v>
+        <v>-8.411849116000003</v>
       </c>
       <c r="P32">
-        <v>-28.69067292000001</v>
+        <v>-29.82382868400001</v>
       </c>
       <c r="Q32">
-        <v>7.509327079999991</v>
+        <v>6.376171315999994</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09503644440771623</v>
+        <v>0.09575001606579908</v>
       </c>
       <c r="T32">
-        <v>1.137100332741714</v>
+        <v>1.153580047708986</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03432537805985157</v>
+        <v>0.03321810779985636</v>
       </c>
       <c r="W32">
-        <v>0.227706075853487</v>
+        <v>0.2279671701807939</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.156024445726598</v>
+        <v>0.1509913990902562</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1367373338414475</v>
+        <v>0.1386373338414475</v>
       </c>
       <c r="C33">
-        <v>43.93234364839702</v>
+        <v>33.58149526696604</v>
       </c>
       <c r="D33">
-        <v>204.723343648397</v>
+        <v>200.5334952669661</v>
       </c>
       <c r="E33">
-        <v>9.091000000000008</v>
+        <v>15.25200000000001</v>
       </c>
       <c r="F33">
-        <v>190.991</v>
+        <v>197.152</v>
       </c>
       <c r="G33">
         <v>30.2</v>
@@ -4353,37 +4353,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M33">
-        <v>45.0356778</v>
+        <v>46.48844160000001</v>
       </c>
       <c r="N33">
-        <v>-38.23567780000001</v>
+        <v>-39.68844160000002</v>
       </c>
       <c r="O33">
-        <v>-8.411849116000003</v>
+        <v>-8.731457152000004</v>
       </c>
       <c r="P33">
-        <v>-29.82382868400001</v>
+        <v>-30.95698444800001</v>
       </c>
       <c r="Q33">
-        <v>6.376171315999994</v>
+        <v>5.243015551999989</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09575001606579908</v>
+        <v>0.09648457512559025</v>
       </c>
       <c r="T33">
-        <v>1.153580047708986</v>
+        <v>1.170544460175294</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03321810779985636</v>
+        <v>0.03218004193111084</v>
       </c>
       <c r="W33">
-        <v>0.2279671701807939</v>
+        <v>0.2282119461126441</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1509913990902562</v>
+        <v>0.1462729178686857</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4399,22 +4399,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1386373338414475</v>
+        <v>0.1405373338414475</v>
       </c>
       <c r="C34">
-        <v>33.58149526696604</v>
+        <v>23.39870548718508</v>
       </c>
       <c r="D34">
-        <v>200.5334952669661</v>
+        <v>196.5117054871851</v>
       </c>
       <c r="E34">
-        <v>15.25200000000001</v>
+        <v>21.41300000000001</v>
       </c>
       <c r="F34">
-        <v>197.152</v>
+        <v>203.313</v>
       </c>
       <c r="G34">
         <v>30.2</v>
@@ -4435,37 +4435,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M34">
-        <v>46.48844160000001</v>
+        <v>47.94120540000001</v>
       </c>
       <c r="N34">
-        <v>-39.68844160000002</v>
+        <v>-41.14120540000002</v>
       </c>
       <c r="O34">
-        <v>-8.731457152000004</v>
+        <v>-9.051065188000004</v>
       </c>
       <c r="P34">
-        <v>-30.95698444800001</v>
+        <v>-32.09014021200002</v>
       </c>
       <c r="Q34">
-        <v>5.243015551999989</v>
+        <v>4.109859787999987</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09648457512559025</v>
+        <v>0.09724106132149457</v>
       </c>
       <c r="T34">
-        <v>1.170544460175294</v>
+        <v>1.188015273013732</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03218004193111084</v>
+        <v>0.0312048891453196</v>
       </c>
       <c r="W34">
-        <v>0.2282119461126441</v>
+        <v>0.2284418871395336</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1462729178686857</v>
+        <v>0.1418404052059982</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4481,22 +4481,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1405373338414475</v>
+        <v>0.1424373338414475</v>
       </c>
       <c r="C35">
-        <v>23.39870548718508</v>
+        <v>13.37406163875025</v>
       </c>
       <c r="D35">
-        <v>196.5117054871851</v>
+        <v>192.6480616387503</v>
       </c>
       <c r="E35">
-        <v>21.41300000000001</v>
+        <v>27.57400000000001</v>
       </c>
       <c r="F35">
-        <v>203.313</v>
+        <v>209.474</v>
       </c>
       <c r="G35">
         <v>30.2</v>
@@ -4517,37 +4517,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M35">
-        <v>47.94120540000001</v>
+        <v>49.39396920000001</v>
       </c>
       <c r="N35">
-        <v>-41.14120540000002</v>
+        <v>-42.59396920000002</v>
       </c>
       <c r="O35">
-        <v>-9.051065188000004</v>
+        <v>-9.370673224000004</v>
       </c>
       <c r="P35">
-        <v>-32.09014021200002</v>
+        <v>-33.22329597600002</v>
       </c>
       <c r="Q35">
-        <v>4.109859787999987</v>
+        <v>2.976704023999986</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09724106132149457</v>
+        <v>0.09802047134151723</v>
       </c>
       <c r="T35">
-        <v>1.188015273013732</v>
+        <v>1.206015504423031</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0312048891453196</v>
+        <v>0.03028709828810432</v>
       </c>
       <c r="W35">
-        <v>0.2284418871395336</v>
+        <v>0.228658302223665</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1418404052059982</v>
+        <v>0.1376686285822923</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4563,22 +4563,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1424373338414475</v>
+        <v>0.1443373338414475</v>
       </c>
       <c r="C36">
-        <v>13.37406163875025</v>
+        <v>3.498415597052002</v>
       </c>
       <c r="D36">
-        <v>192.6480616387503</v>
+        <v>188.933415597052</v>
       </c>
       <c r="E36">
-        <v>27.57400000000001</v>
+        <v>33.73500000000001</v>
       </c>
       <c r="F36">
-        <v>209.474</v>
+        <v>215.635</v>
       </c>
       <c r="G36">
         <v>30.2</v>
@@ -4599,37 +4599,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M36">
-        <v>49.39396920000001</v>
+        <v>50.84673300000001</v>
       </c>
       <c r="N36">
-        <v>-42.59396920000002</v>
+        <v>-44.04673300000002</v>
       </c>
       <c r="O36">
-        <v>-9.370673224000004</v>
+        <v>-9.690281260000004</v>
       </c>
       <c r="P36">
-        <v>-33.22329597600002</v>
+        <v>-34.35645174000001</v>
       </c>
       <c r="Q36">
-        <v>2.976704023999986</v>
+        <v>1.843548259999992</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09802047134151723</v>
+        <v>0.0988238632083098</v>
       </c>
       <c r="T36">
-        <v>1.206015504423031</v>
+        <v>1.224569589106462</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03028709828810432</v>
+        <v>0.02942175262272991</v>
       </c>
       <c r="W36">
-        <v>0.228658302223665</v>
+        <v>0.2288623507315603</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1376686285822923</v>
+        <v>0.1337352391942269</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4645,22 +4645,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1443373338414475</v>
+        <v>0.1462373338414475</v>
       </c>
       <c r="C37">
-        <v>3.498415597052002</v>
+        <v>-6.23668853240531</v>
       </c>
       <c r="D37">
-        <v>188.933415597052</v>
+        <v>185.3593114675947</v>
       </c>
       <c r="E37">
-        <v>33.73500000000001</v>
+        <v>39.89600000000002</v>
       </c>
       <c r="F37">
-        <v>215.635</v>
+        <v>221.796</v>
       </c>
       <c r="G37">
         <v>30.2</v>
@@ -4681,37 +4681,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M37">
-        <v>50.84673300000001</v>
+        <v>52.29949680000001</v>
       </c>
       <c r="N37">
-        <v>-44.04673300000002</v>
+        <v>-45.49949680000002</v>
       </c>
       <c r="O37">
-        <v>-9.690281260000004</v>
+        <v>-10.009889296</v>
       </c>
       <c r="P37">
-        <v>-34.35645174000001</v>
+        <v>-35.48960750400001</v>
       </c>
       <c r="Q37">
-        <v>1.843548259999992</v>
+        <v>0.7103924959999901</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0988238632083098</v>
+        <v>0.09965236107093964</v>
       </c>
       <c r="T37">
-        <v>1.224569589106462</v>
+        <v>1.24370348893625</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02942175262272991</v>
+        <v>0.02860448171654297</v>
       </c>
       <c r="W37">
-        <v>0.2288623507315603</v>
+        <v>0.2290550632112392</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1337352391942269</v>
+        <v>0.1300203714388317</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4727,22 +4727,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1462373338414475</v>
+        <v>0.1481373338414474</v>
       </c>
       <c r="C38">
-        <v>-6.236688532405282</v>
+        <v>-15.83907867389618</v>
       </c>
       <c r="D38">
-        <v>185.3593114675947</v>
+        <v>181.9179213261038</v>
       </c>
       <c r="E38">
-        <v>39.89599999999999</v>
+        <v>46.05699999999999</v>
       </c>
       <c r="F38">
-        <v>221.796</v>
+        <v>227.957</v>
       </c>
       <c r="G38">
         <v>30.2</v>
@@ -4763,37 +4763,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M38">
-        <v>52.2994968</v>
+        <v>53.7522606</v>
       </c>
       <c r="N38">
-        <v>-45.49949680000001</v>
+        <v>-46.95226060000001</v>
       </c>
       <c r="O38">
-        <v>-10.009889296</v>
+        <v>-10.329497332</v>
       </c>
       <c r="P38">
-        <v>-35.48960750400001</v>
+        <v>-36.62276326800001</v>
       </c>
       <c r="Q38">
-        <v>0.7103924959999972</v>
+        <v>-0.4227632680000042</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09965236107093964</v>
+        <v>0.100507160453018</v>
       </c>
       <c r="T38">
-        <v>1.24370348893625</v>
+        <v>1.263444814157461</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02860448171654298</v>
+        <v>0.02783138761609587</v>
       </c>
       <c r="W38">
-        <v>0.2290550632112392</v>
+        <v>0.2292373588001246</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1300203714388317</v>
+        <v>0.1265063073458903</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4809,22 +4809,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1481373338414474</v>
+        <v>0.1500373338414475</v>
       </c>
       <c r="C39">
-        <v>-15.83907867389618</v>
+        <v>-25.316012013532</v>
       </c>
       <c r="D39">
-        <v>181.9179213261038</v>
+        <v>178.601987986468</v>
       </c>
       <c r="E39">
-        <v>46.05699999999999</v>
+        <v>52.21800000000002</v>
       </c>
       <c r="F39">
-        <v>227.957</v>
+        <v>234.118</v>
       </c>
       <c r="G39">
         <v>30.2</v>
@@ -4845,37 +4845,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M39">
-        <v>53.7522606</v>
+        <v>55.20502440000001</v>
       </c>
       <c r="N39">
-        <v>-46.95226060000001</v>
+        <v>-48.40502440000002</v>
       </c>
       <c r="O39">
-        <v>-10.329497332</v>
+        <v>-10.649105368</v>
       </c>
       <c r="P39">
-        <v>-36.62276326800001</v>
+        <v>-37.75591903200001</v>
       </c>
       <c r="Q39">
-        <v>-0.4227632680000042</v>
+        <v>-1.555919032000006</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.100507160453018</v>
+        <v>0.1013895340087119</v>
       </c>
       <c r="T39">
-        <v>1.263444814157461</v>
+        <v>1.283822956321291</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02783138761609587</v>
+        <v>0.02709898267883018</v>
       </c>
       <c r="W39">
-        <v>0.2292373588001246</v>
+        <v>0.2294100598843319</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1265063073458903</v>
+        <v>0.1231771939946826</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4891,22 +4891,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1500373338414475</v>
+        <v>0.1519373338414475</v>
       </c>
       <c r="C40">
-        <v>-25.316012013532</v>
+        <v>-34.67422608413622</v>
       </c>
       <c r="D40">
-        <v>178.601987986468</v>
+        <v>175.4047739158638</v>
       </c>
       <c r="E40">
-        <v>52.21800000000002</v>
+        <v>58.37900000000002</v>
       </c>
       <c r="F40">
-        <v>234.118</v>
+        <v>240.279</v>
       </c>
       <c r="G40">
         <v>30.2</v>
@@ -4927,37 +4927,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M40">
-        <v>55.20502440000001</v>
+        <v>56.65778820000001</v>
       </c>
       <c r="N40">
-        <v>-48.40502440000002</v>
+        <v>-49.85778820000002</v>
       </c>
       <c r="O40">
-        <v>-10.649105368</v>
+        <v>-10.968713404</v>
       </c>
       <c r="P40">
-        <v>-37.75591903200001</v>
+        <v>-38.88907479600001</v>
       </c>
       <c r="Q40">
-        <v>-1.555919032000006</v>
+        <v>-2.689074796000007</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1013895340087119</v>
+        <v>0.1023008378449203</v>
       </c>
       <c r="T40">
-        <v>1.283822956321291</v>
+        <v>1.304869234293771</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02709898267883018</v>
+        <v>0.02640413696911659</v>
       </c>
       <c r="W40">
-        <v>0.2294100598843319</v>
+        <v>0.2295739045026823</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1231771939946826</v>
+        <v>0.1200188044050754</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1519373338414475</v>
+        <v>0.1538373338414475</v>
       </c>
       <c r="C41">
-        <v>-34.67422608413622</v>
+        <v>-43.91998445969222</v>
       </c>
       <c r="D41">
-        <v>175.4047739158638</v>
+        <v>172.3200155403078</v>
       </c>
       <c r="E41">
-        <v>58.37900000000002</v>
+        <v>64.54000000000002</v>
       </c>
       <c r="F41">
-        <v>240.279</v>
+        <v>246.44</v>
       </c>
       <c r="G41">
         <v>30.2</v>
@@ -5009,37 +5009,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M41">
-        <v>56.65778820000001</v>
+        <v>58.11055200000001</v>
       </c>
       <c r="N41">
-        <v>-49.85778820000002</v>
+        <v>-51.31055200000002</v>
       </c>
       <c r="O41">
-        <v>-10.968713404</v>
+        <v>-11.28832144</v>
       </c>
       <c r="P41">
-        <v>-38.88907479600001</v>
+        <v>-40.02223056000001</v>
       </c>
       <c r="Q41">
-        <v>-2.689074796000007</v>
+        <v>-3.822230560000008</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1023008378449203</v>
+        <v>0.103242518475669</v>
       </c>
       <c r="T41">
-        <v>1.304869234293771</v>
+        <v>1.326617054865334</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02640413696911659</v>
+        <v>0.02574403354488868</v>
       </c>
       <c r="W41">
-        <v>0.2295739045026823</v>
+        <v>0.2297295568901153</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1200188044050754</v>
+        <v>0.1170183342949486</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5055,22 +5055,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1538373338414475</v>
+        <v>0.1557373338414475</v>
       </c>
       <c r="C42">
-        <v>-43.91998445969222</v>
+        <v>-53.05911771148428</v>
       </c>
       <c r="D42">
-        <v>172.3200155403078</v>
+        <v>169.3418822885158</v>
       </c>
       <c r="E42">
-        <v>64.54000000000002</v>
+        <v>70.70100000000002</v>
       </c>
       <c r="F42">
-        <v>246.44</v>
+        <v>252.601</v>
       </c>
       <c r="G42">
         <v>30.2</v>
@@ -5091,37 +5091,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M42">
-        <v>58.11055200000001</v>
+        <v>59.56331580000001</v>
       </c>
       <c r="N42">
-        <v>-51.31055200000002</v>
+        <v>-52.76331580000002</v>
       </c>
       <c r="O42">
-        <v>-11.28832144</v>
+        <v>-11.607929476</v>
       </c>
       <c r="P42">
-        <v>-40.02223056000001</v>
+        <v>-41.15538632400002</v>
       </c>
       <c r="Q42">
-        <v>-3.822230560000008</v>
+        <v>-4.955386324000017</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.103242518475669</v>
+        <v>0.1042161204837311</v>
       </c>
       <c r="T42">
-        <v>1.326617054865334</v>
+        <v>1.34910208969356</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02574403354488868</v>
+        <v>0.02511613028769626</v>
       </c>
       <c r="W42">
-        <v>0.2297295568901153</v>
+        <v>0.2298776164781612</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1170183342949486</v>
+        <v>0.1141642285804376</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5137,22 +5137,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1557373338414475</v>
+        <v>0.1576373338414475</v>
       </c>
       <c r="C43">
-        <v>-53.05911771148428</v>
+        <v>-62.09706018942575</v>
       </c>
       <c r="D43">
-        <v>169.3418822885158</v>
+        <v>166.4649398105743</v>
       </c>
       <c r="E43">
-        <v>70.70100000000002</v>
+        <v>76.86200000000005</v>
       </c>
       <c r="F43">
-        <v>252.601</v>
+        <v>258.7620000000001</v>
       </c>
       <c r="G43">
         <v>30.2</v>
@@ -5173,37 +5173,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M43">
-        <v>59.56331580000001</v>
+        <v>61.01607960000002</v>
       </c>
       <c r="N43">
-        <v>-52.76331580000002</v>
+        <v>-54.21607960000003</v>
       </c>
       <c r="O43">
-        <v>-11.607929476</v>
+        <v>-11.92753751200001</v>
       </c>
       <c r="P43">
-        <v>-41.15538632400002</v>
+        <v>-42.28854208800002</v>
       </c>
       <c r="Q43">
-        <v>-4.955386324000017</v>
+        <v>-6.088542088000018</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1042161204837311</v>
+        <v>0.1052232949748299</v>
       </c>
       <c r="T43">
-        <v>1.34910208969356</v>
+        <v>1.372362470550345</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02511613028769626</v>
+        <v>0.02451812718560826</v>
       </c>
       <c r="W43">
-        <v>0.2298776164781612</v>
+        <v>0.2300186256096336</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1141642285804376</v>
+        <v>0.1114460326618557</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5219,22 +5219,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1576373338414475</v>
+        <v>0.1595373338414475</v>
       </c>
       <c r="C44">
-        <v>-62.09706018942569</v>
+        <v>-71.03888311675928</v>
       </c>
       <c r="D44">
-        <v>166.4649398105743</v>
+        <v>163.6841168832407</v>
       </c>
       <c r="E44">
-        <v>76.86199999999999</v>
+        <v>83.023</v>
       </c>
       <c r="F44">
-        <v>258.762</v>
+        <v>264.923</v>
       </c>
       <c r="G44">
         <v>30.2</v>
@@ -5255,37 +5255,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M44">
-        <v>61.0160796</v>
+        <v>62.4688434</v>
       </c>
       <c r="N44">
-        <v>-54.21607960000001</v>
+        <v>-55.66884340000001</v>
       </c>
       <c r="O44">
-        <v>-11.927537512</v>
+        <v>-12.247145548</v>
       </c>
       <c r="P44">
-        <v>-42.28854208800001</v>
+        <v>-43.42169785200001</v>
       </c>
       <c r="Q44">
-        <v>-6.088542088000011</v>
+        <v>-7.221697852000005</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1052232949748299</v>
+        <v>0.1062658089217568</v>
       </c>
       <c r="T44">
-        <v>1.372362470550345</v>
+        <v>1.396439005121404</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02451812718560826</v>
+        <v>0.02394793818129179</v>
       </c>
       <c r="W44">
-        <v>0.2300186256096336</v>
+        <v>0.2301530761768514</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1114460326618557</v>
+        <v>0.1088542644604172</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5301,22 +5301,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1595373338414475</v>
+        <v>0.1614373338414475</v>
       </c>
       <c r="C45">
-        <v>-71.03888311675928</v>
+        <v>-79.88932442214752</v>
       </c>
       <c r="D45">
-        <v>163.6841168832407</v>
+        <v>160.9946755778525</v>
       </c>
       <c r="E45">
-        <v>83.023</v>
+        <v>89.184</v>
       </c>
       <c r="F45">
-        <v>264.923</v>
+        <v>271.084</v>
       </c>
       <c r="G45">
         <v>30.2</v>
@@ -5337,37 +5337,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M45">
-        <v>62.4688434</v>
+        <v>63.9216072</v>
       </c>
       <c r="N45">
-        <v>-55.66884340000001</v>
+        <v>-57.12160720000001</v>
       </c>
       <c r="O45">
-        <v>-12.247145548</v>
+        <v>-12.566753584</v>
       </c>
       <c r="P45">
-        <v>-43.42169785200001</v>
+        <v>-44.55485361600001</v>
       </c>
       <c r="Q45">
-        <v>-7.221697852000005</v>
+        <v>-8.354853616000007</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1062658089217568</v>
+        <v>0.1073455555096453</v>
       </c>
       <c r="T45">
-        <v>1.396439005121404</v>
+        <v>1.421375415927143</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02394793818129179</v>
+        <v>0.02340366685898971</v>
       </c>
       <c r="W45">
-        <v>0.2301530761768514</v>
+        <v>0.2302814153546502</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1088542644604172</v>
+        <v>0.1063803039044987</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1614373338414475</v>
+        <v>0.1633373338414474</v>
       </c>
       <c r="C46">
-        <v>-79.88932442214752</v>
+        <v>-88.65281567833466</v>
       </c>
       <c r="D46">
-        <v>160.9946755778525</v>
+        <v>158.3921843216654</v>
       </c>
       <c r="E46">
-        <v>89.184</v>
+        <v>95.345</v>
       </c>
       <c r="F46">
-        <v>271.084</v>
+        <v>277.245</v>
       </c>
       <c r="G46">
         <v>30.2</v>
@@ -5419,37 +5419,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M46">
-        <v>63.9216072</v>
+        <v>65.37437100000001</v>
       </c>
       <c r="N46">
-        <v>-57.12160720000001</v>
+        <v>-58.57437100000002</v>
       </c>
       <c r="O46">
-        <v>-12.566753584</v>
+        <v>-12.88636162</v>
       </c>
       <c r="P46">
-        <v>-44.55485361600001</v>
+        <v>-45.68800938000002</v>
       </c>
       <c r="Q46">
-        <v>-8.354853616000007</v>
+        <v>-9.488009380000015</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1073455555096453</v>
+        <v>0.1084645656098207</v>
       </c>
       <c r="T46">
-        <v>1.421375415927143</v>
+        <v>1.447218605307637</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02340366685898971</v>
+        <v>0.02288358537323438</v>
       </c>
       <c r="W46">
-        <v>0.2302814153546502</v>
+        <v>0.2304040505689913</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1063803039044987</v>
+        <v>0.1040162971510653</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5465,22 +5465,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1633373338414474</v>
+        <v>0.1652373338414475</v>
       </c>
       <c r="C47">
-        <v>-88.65281567833466</v>
+        <v>-97.33350646957982</v>
       </c>
       <c r="D47">
-        <v>158.3921843216654</v>
+        <v>155.8724935304202</v>
       </c>
       <c r="E47">
-        <v>95.345</v>
+        <v>101.506</v>
       </c>
       <c r="F47">
-        <v>277.245</v>
+        <v>283.406</v>
       </c>
       <c r="G47">
         <v>30.2</v>
@@ -5501,37 +5501,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M47">
-        <v>65.37437100000001</v>
+        <v>66.82713480000001</v>
       </c>
       <c r="N47">
-        <v>-58.57437100000002</v>
+        <v>-60.02713480000002</v>
       </c>
       <c r="O47">
-        <v>-12.88636162</v>
+        <v>-13.205969656</v>
       </c>
       <c r="P47">
-        <v>-45.68800938000002</v>
+        <v>-46.82116514400002</v>
       </c>
       <c r="Q47">
-        <v>-9.488009380000015</v>
+        <v>-10.62116514400002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1084645656098207</v>
+        <v>0.109625020528521</v>
       </c>
       <c r="T47">
-        <v>1.447218605307637</v>
+        <v>1.474018949850371</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02288358537323438</v>
+        <v>0.02238611612599015</v>
       </c>
       <c r="W47">
-        <v>0.2304040505689913</v>
+        <v>0.2305213538174915</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1040162971510653</v>
+        <v>0.1017550732999553</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5547,22 +5547,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1652373338414475</v>
+        <v>0.1671373338414475</v>
       </c>
       <c r="C48">
-        <v>-97.33350646957982</v>
+        <v>-105.9352864696974</v>
       </c>
       <c r="D48">
-        <v>155.8724935304202</v>
+        <v>153.4317135303026</v>
       </c>
       <c r="E48">
-        <v>101.506</v>
+        <v>107.667</v>
       </c>
       <c r="F48">
-        <v>283.406</v>
+        <v>289.567</v>
       </c>
       <c r="G48">
         <v>30.2</v>
@@ -5583,37 +5583,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M48">
-        <v>66.82713480000001</v>
+        <v>68.27989860000001</v>
       </c>
       <c r="N48">
-        <v>-60.02713480000002</v>
+        <v>-61.47989860000002</v>
       </c>
       <c r="O48">
-        <v>-13.205969656</v>
+        <v>-13.525577692</v>
       </c>
       <c r="P48">
-        <v>-46.82116514400002</v>
+        <v>-47.95432090800001</v>
       </c>
       <c r="Q48">
-        <v>-10.62116514400002</v>
+        <v>-11.75432090800001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.109625020528521</v>
+        <v>0.1108292661988705</v>
       </c>
       <c r="T48">
-        <v>1.474018949850371</v>
+        <v>1.501830628149434</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02238611612599015</v>
+        <v>0.02190981578288398</v>
       </c>
       <c r="W48">
-        <v>0.2305213538174915</v>
+        <v>0.230633665438396</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1017550732999553</v>
+        <v>0.0995900717403817</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5629,22 +5629,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1671373338414475</v>
+        <v>0.1690373338414475</v>
       </c>
       <c r="C49">
-        <v>-105.9352864696974</v>
+        <v>-114.4618054777817</v>
       </c>
       <c r="D49">
-        <v>153.4317135303026</v>
+        <v>151.0661945222183</v>
       </c>
       <c r="E49">
-        <v>107.667</v>
+        <v>113.828</v>
       </c>
       <c r="F49">
-        <v>289.567</v>
+        <v>295.728</v>
       </c>
       <c r="G49">
         <v>30.2</v>
@@ -5665,37 +5665,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M49">
-        <v>68.27989860000001</v>
+        <v>69.73266240000001</v>
       </c>
       <c r="N49">
-        <v>-61.47989860000002</v>
+        <v>-62.93266240000002</v>
       </c>
       <c r="O49">
-        <v>-13.525577692</v>
+        <v>-13.845185728</v>
       </c>
       <c r="P49">
-        <v>-47.95432090800001</v>
+        <v>-49.08747667200002</v>
       </c>
       <c r="Q49">
-        <v>-11.75432090800001</v>
+        <v>-12.88747667200001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1108292661988705</v>
+        <v>0.1120798290103872</v>
       </c>
       <c r="T49">
-        <v>1.501830628149434</v>
+        <v>1.530711986383077</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02190981578288398</v>
+        <v>0.02145336128740723</v>
       </c>
       <c r="W49">
-        <v>0.230633665438396</v>
+        <v>0.2307412974084294</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.0995900717403817</v>
+        <v>0.09751527857912379</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5711,22 +5711,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1690373338414475</v>
+        <v>0.1709373338414475</v>
       </c>
       <c r="C50">
-        <v>-114.4618054777817</v>
+        <v>-122.916491628678</v>
       </c>
       <c r="D50">
-        <v>151.0661945222183</v>
+        <v>148.772508371322</v>
       </c>
       <c r="E50">
-        <v>113.828</v>
+        <v>119.989</v>
       </c>
       <c r="F50">
-        <v>295.728</v>
+        <v>301.889</v>
       </c>
       <c r="G50">
         <v>30.2</v>
@@ -5747,37 +5747,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M50">
-        <v>69.73266240000001</v>
+        <v>71.18542620000001</v>
       </c>
       <c r="N50">
-        <v>-62.93266240000002</v>
+        <v>-64.38542620000001</v>
       </c>
       <c r="O50">
-        <v>-13.845185728</v>
+        <v>-14.164793764</v>
       </c>
       <c r="P50">
-        <v>-49.08747667200002</v>
+        <v>-50.22063243600001</v>
       </c>
       <c r="Q50">
-        <v>-12.88747667200001</v>
+        <v>-14.02063243600001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1120798290103872</v>
+        <v>0.113379433500787</v>
       </c>
       <c r="T50">
-        <v>1.530711986383077</v>
+        <v>1.560725946900392</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02145336128740723</v>
+        <v>0.02101553758766422</v>
       </c>
       <c r="W50">
-        <v>0.2307412974084294</v>
+        <v>0.2308445362368288</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.09751527857912379</v>
+        <v>0.09552517085301926</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5793,22 +5793,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1709373338414475</v>
+        <v>0.1728373338414474</v>
       </c>
       <c r="C51">
-        <v>-122.916491628678</v>
+        <v>-131.3025679692938</v>
       </c>
       <c r="D51">
-        <v>148.772508371322</v>
+        <v>146.5474320307063</v>
       </c>
       <c r="E51">
-        <v>119.989</v>
+        <v>126.15</v>
       </c>
       <c r="F51">
-        <v>301.889</v>
+        <v>308.05</v>
       </c>
       <c r="G51">
         <v>30.2</v>
@@ -5829,37 +5829,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M51">
-        <v>71.18542620000001</v>
+        <v>72.63819000000001</v>
       </c>
       <c r="N51">
-        <v>-64.38542620000001</v>
+        <v>-65.83819000000003</v>
       </c>
       <c r="O51">
-        <v>-14.164793764</v>
+        <v>-14.48440180000001</v>
       </c>
       <c r="P51">
-        <v>-50.22063243600001</v>
+        <v>-51.35378820000002</v>
       </c>
       <c r="Q51">
-        <v>-14.02063243600001</v>
+        <v>-15.15378820000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.113379433500787</v>
+        <v>0.1147310221708027</v>
       </c>
       <c r="T51">
-        <v>1.560725946900392</v>
+        <v>1.5919404658384</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02101553758766422</v>
+        <v>0.02059522683591094</v>
       </c>
       <c r="W51">
-        <v>0.2308445362368288</v>
+        <v>0.2309436455120922</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.09552517085301926</v>
+        <v>0.0936146674359587</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5875,22 +5875,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1728373338414474</v>
+        <v>0.1747373338414475</v>
       </c>
       <c r="C52">
-        <v>-131.3025679692938</v>
+        <v>-139.6230675693145</v>
       </c>
       <c r="D52">
-        <v>146.5474320307063</v>
+        <v>144.3879324306855</v>
       </c>
       <c r="E52">
-        <v>126.15</v>
+        <v>132.311</v>
       </c>
       <c r="F52">
-        <v>308.05</v>
+        <v>314.211</v>
       </c>
       <c r="G52">
         <v>30.2</v>
@@ -5911,37 +5911,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M52">
-        <v>72.63819000000001</v>
+        <v>74.09095380000001</v>
       </c>
       <c r="N52">
-        <v>-65.83819000000003</v>
+        <v>-67.29095380000001</v>
       </c>
       <c r="O52">
-        <v>-14.48440180000001</v>
+        <v>-14.804009836</v>
       </c>
       <c r="P52">
-        <v>-51.35378820000002</v>
+        <v>-52.48694396400001</v>
       </c>
       <c r="Q52">
-        <v>-15.15378820000002</v>
+        <v>-16.286943964</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1147310221708027</v>
+        <v>0.1161377777253089</v>
       </c>
       <c r="T52">
-        <v>1.5919404658384</v>
+        <v>1.624429046773878</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02059522683591094</v>
+        <v>0.02019139885873622</v>
       </c>
       <c r="W52">
-        <v>0.2309436455120922</v>
+        <v>0.23103886814911</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.0936146674359587</v>
+        <v>0.09177908572152838</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5957,22 +5957,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1747373338414475</v>
+        <v>0.1766373338414475</v>
       </c>
       <c r="C53">
-        <v>-139.6230675693145</v>
+        <v>-147.8808473153062</v>
       </c>
       <c r="D53">
-        <v>144.3879324306855</v>
+        <v>142.2911526846938</v>
       </c>
       <c r="E53">
-        <v>132.311</v>
+        <v>138.472</v>
       </c>
       <c r="F53">
-        <v>314.211</v>
+        <v>320.372</v>
       </c>
       <c r="G53">
         <v>30.2</v>
@@ -5993,37 +5993,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M53">
-        <v>74.09095380000001</v>
+        <v>75.54371760000001</v>
       </c>
       <c r="N53">
-        <v>-67.29095380000001</v>
+        <v>-68.74371760000002</v>
       </c>
       <c r="O53">
-        <v>-14.804009836</v>
+        <v>-15.12361787200001</v>
       </c>
       <c r="P53">
-        <v>-52.48694396400001</v>
+        <v>-53.62009972800002</v>
       </c>
       <c r="Q53">
-        <v>-16.286943964</v>
+        <v>-17.42009972800002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1161377777253089</v>
+        <v>0.1176031480945862</v>
       </c>
       <c r="T53">
-        <v>1.624429046773878</v>
+        <v>1.658271318581667</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02019139885873622</v>
+        <v>0.01980310272683744</v>
       </c>
       <c r="W53">
-        <v>0.23103886814911</v>
+        <v>0.2311304283770117</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.09177908572152838</v>
+        <v>0.09001410330380644</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6039,22 +6039,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1766373338414475</v>
+        <v>0.1785373338414475</v>
       </c>
       <c r="C54">
-        <v>-147.8808473153062</v>
+        <v>-156.0786005201269</v>
       </c>
       <c r="D54">
-        <v>142.2911526846938</v>
+        <v>140.2543994798732</v>
       </c>
       <c r="E54">
-        <v>138.472</v>
+        <v>144.633</v>
       </c>
       <c r="F54">
-        <v>320.372</v>
+        <v>326.533</v>
       </c>
       <c r="G54">
         <v>30.2</v>
@@ -6075,37 +6075,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M54">
-        <v>75.54371760000001</v>
+        <v>76.99648140000001</v>
       </c>
       <c r="N54">
-        <v>-68.74371760000002</v>
+        <v>-70.19648140000001</v>
       </c>
       <c r="O54">
-        <v>-15.12361787200001</v>
+        <v>-15.443225908</v>
       </c>
       <c r="P54">
-        <v>-53.62009972800002</v>
+        <v>-54.75325549200001</v>
       </c>
       <c r="Q54">
-        <v>-17.42009972800002</v>
+        <v>-18.55325549200001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1176031480945862</v>
+        <v>0.1191308746497901</v>
       </c>
       <c r="T54">
-        <v>1.658271318581667</v>
+        <v>1.693553687062128</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01980310272683744</v>
+        <v>0.01942945927916126</v>
       </c>
       <c r="W54">
-        <v>0.2311304283770117</v>
+        <v>0.2312185335019738</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.09001410330380644</v>
+        <v>0.0883157239961877</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6121,22 +6121,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1785373338414475</v>
+        <v>0.1804373338414475</v>
       </c>
       <c r="C55">
-        <v>-156.0786005201269</v>
+        <v>-164.2188684646747</v>
       </c>
       <c r="D55">
-        <v>140.2543994798732</v>
+        <v>138.2751315353253</v>
       </c>
       <c r="E55">
-        <v>144.633</v>
+        <v>150.794</v>
       </c>
       <c r="F55">
-        <v>326.533</v>
+        <v>332.694</v>
       </c>
       <c r="G55">
         <v>30.2</v>
@@ -6157,37 +6157,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M55">
-        <v>76.99648140000001</v>
+        <v>78.44924520000001</v>
       </c>
       <c r="N55">
-        <v>-70.19648140000001</v>
+        <v>-71.64924520000002</v>
       </c>
       <c r="O55">
-        <v>-15.443225908</v>
+        <v>-15.76283394400001</v>
       </c>
       <c r="P55">
-        <v>-54.75325549200001</v>
+        <v>-55.88641125600002</v>
       </c>
       <c r="Q55">
-        <v>-18.55325549200001</v>
+        <v>-19.68641125600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1191308746497901</v>
+        <v>0.1207250240986986</v>
       </c>
       <c r="T55">
-        <v>1.693553687062128</v>
+        <v>1.730370071563479</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01942945927916126</v>
+        <v>0.01906965447769531</v>
       </c>
       <c r="W55">
-        <v>0.2312185335019738</v>
+        <v>0.2313033754741595</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.0883157239961877</v>
+        <v>0.08668024762588766</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6203,22 +6203,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1804373338414475</v>
+        <v>0.1823373338414475</v>
       </c>
       <c r="C56">
-        <v>-164.2188684646747</v>
+        <v>-172.3040509759738</v>
       </c>
       <c r="D56">
-        <v>138.2751315353253</v>
+        <v>136.3509490240262</v>
       </c>
       <c r="E56">
-        <v>150.794</v>
+        <v>156.955</v>
       </c>
       <c r="F56">
-        <v>332.694</v>
+        <v>338.855</v>
       </c>
       <c r="G56">
         <v>30.2</v>
@@ -6239,37 +6239,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M56">
-        <v>78.44924520000001</v>
+        <v>79.90200900000001</v>
       </c>
       <c r="N56">
-        <v>-71.64924520000002</v>
+        <v>-73.10200900000001</v>
       </c>
       <c r="O56">
-        <v>-15.76283394400001</v>
+        <v>-16.08244198</v>
       </c>
       <c r="P56">
-        <v>-55.88641125600002</v>
+        <v>-57.01956702000001</v>
       </c>
       <c r="Q56">
-        <v>-19.68641125600001</v>
+        <v>-20.81956702000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1207250240986986</v>
+        <v>0.1223900246342253</v>
       </c>
       <c r="T56">
-        <v>1.730370071563479</v>
+        <v>1.768822739820445</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01906965447769531</v>
+        <v>0.01872293348719176</v>
       </c>
       <c r="W56">
-        <v>0.2313033754741595</v>
+        <v>0.2313851322837202</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.08668024762588766</v>
+        <v>0.08510424312359899</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6285,22 +6285,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1823373338414475</v>
+        <v>0.1842373338414475</v>
       </c>
       <c r="C57">
-        <v>-172.3040509759738</v>
+        <v>-180.3364161341785</v>
       </c>
       <c r="D57">
-        <v>136.3509490240262</v>
+        <v>134.4795838658215</v>
       </c>
       <c r="E57">
-        <v>156.955</v>
+        <v>163.116</v>
       </c>
       <c r="F57">
-        <v>338.855</v>
+        <v>345.016</v>
       </c>
       <c r="G57">
         <v>30.2</v>
@@ -6321,37 +6321,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M57">
-        <v>79.90200900000001</v>
+        <v>81.35477280000001</v>
       </c>
       <c r="N57">
-        <v>-73.10200900000001</v>
+        <v>-74.55477280000002</v>
       </c>
       <c r="O57">
-        <v>-16.08244198</v>
+        <v>-16.402050016</v>
       </c>
       <c r="P57">
-        <v>-57.01956702000001</v>
+        <v>-58.15272278400002</v>
       </c>
       <c r="Q57">
-        <v>-20.81956702000001</v>
+        <v>-21.95272278400002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1223900246342253</v>
+        <v>0.1241307070122758</v>
       </c>
       <c r="T57">
-        <v>1.768822739820445</v>
+        <v>1.809023256634546</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01872293348719176</v>
+        <v>0.0183885953892062</v>
       </c>
       <c r="W57">
-        <v>0.2313851322837202</v>
+        <v>0.2314639692072252</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.08510424312359899</v>
+        <v>0.08358452449639175</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6367,22 +6367,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1842373338414475</v>
+        <v>0.1861373338414475</v>
       </c>
       <c r="C58">
-        <v>-180.3364161341785</v>
+        <v>-188.3181091910507</v>
       </c>
       <c r="D58">
-        <v>134.4795838658215</v>
+        <v>132.6588908089494</v>
       </c>
       <c r="E58">
-        <v>163.116</v>
+        <v>169.2770000000001</v>
       </c>
       <c r="F58">
-        <v>345.016</v>
+        <v>351.1770000000001</v>
       </c>
       <c r="G58">
         <v>30.2</v>
@@ -6403,37 +6403,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M58">
-        <v>81.35477280000001</v>
+        <v>82.80753660000002</v>
       </c>
       <c r="N58">
-        <v>-74.55477280000002</v>
+        <v>-76.00753660000004</v>
       </c>
       <c r="O58">
-        <v>-16.402050016</v>
+        <v>-16.72165805200001</v>
       </c>
       <c r="P58">
-        <v>-58.15272278400002</v>
+        <v>-59.28587854800003</v>
       </c>
       <c r="Q58">
-        <v>-21.95272278400002</v>
+        <v>-23.08587854800003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1241307070122758</v>
+        <v>0.1259523513613985</v>
       </c>
       <c r="T58">
-        <v>1.809023256634546</v>
+        <v>1.851093564928372</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0183885953892062</v>
+        <v>0.01806598845255345</v>
       </c>
       <c r="W58">
-        <v>0.2314639692072252</v>
+        <v>0.2315400399228879</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.08358452449639175</v>
+        <v>0.08211812932978835</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1861373338414475</v>
+        <v>0.1880373338414475</v>
       </c>
       <c r="C59">
-        <v>-188.3181091910507</v>
+        <v>-196.2511607736399</v>
       </c>
       <c r="D59">
-        <v>132.6588908089494</v>
+        <v>130.8868392263602</v>
       </c>
       <c r="E59">
-        <v>169.2770000000001</v>
+        <v>175.4380000000001</v>
       </c>
       <c r="F59">
-        <v>351.1770000000001</v>
+        <v>357.3380000000001</v>
       </c>
       <c r="G59">
         <v>30.2</v>
@@ -6485,37 +6485,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M59">
-        <v>82.80753660000002</v>
+        <v>84.26030040000002</v>
       </c>
       <c r="N59">
-        <v>-76.00753660000004</v>
+        <v>-77.46030040000002</v>
       </c>
       <c r="O59">
-        <v>-16.72165805200001</v>
+        <v>-17.041266088</v>
       </c>
       <c r="P59">
-        <v>-59.28587854800003</v>
+        <v>-60.41903431200002</v>
       </c>
       <c r="Q59">
-        <v>-23.08587854800003</v>
+        <v>-24.21903431200002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1259523513613985</v>
+        <v>0.1278607406795271</v>
       </c>
       <c r="T59">
-        <v>1.851093564928372</v>
+        <v>1.895167221236191</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01806598845255345</v>
+        <v>0.01775450589302667</v>
       </c>
       <c r="W59">
-        <v>0.2315400399228879</v>
+        <v>0.2316134875104243</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.08211812932978835</v>
+        <v>0.08070229951375762</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6531,22 +6531,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1880373338414475</v>
+        <v>0.1899373338414475</v>
       </c>
       <c r="C60">
-        <v>-196.2511607736398</v>
+        <v>-204.137494439126</v>
       </c>
       <c r="D60">
-        <v>130.8868392263602</v>
+        <v>129.1615055608739</v>
       </c>
       <c r="E60">
-        <v>175.438</v>
+        <v>181.599</v>
       </c>
       <c r="F60">
-        <v>357.338</v>
+        <v>363.499</v>
       </c>
       <c r="G60">
         <v>30.2</v>
@@ -6567,37 +6567,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M60">
-        <v>84.26030039999999</v>
+        <v>85.71306419999999</v>
       </c>
       <c r="N60">
-        <v>-77.46030039999999</v>
+        <v>-78.91306420000001</v>
       </c>
       <c r="O60">
-        <v>-17.041266088</v>
+        <v>-17.360874124</v>
       </c>
       <c r="P60">
-        <v>-60.41903431199999</v>
+        <v>-61.552190076</v>
       </c>
       <c r="Q60">
-        <v>-24.21903431199999</v>
+        <v>-25.352190076</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.127860740679527</v>
+        <v>0.1298622221595155</v>
       </c>
       <c r="T60">
-        <v>1.895167221236191</v>
+        <v>1.941390811998049</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01775450589302667</v>
+        <v>0.01745358206433131</v>
       </c>
       <c r="W60">
-        <v>0.2316134875104243</v>
+        <v>0.2316844453492307</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.08070229951375774</v>
+        <v>0.07933446392877863</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6613,22 +6613,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1899373338414475</v>
+        <v>0.1918373338414475</v>
       </c>
       <c r="C61">
-        <v>-204.137494439126</v>
+        <v>-211.9789336399136</v>
       </c>
       <c r="D61">
-        <v>129.1615055608739</v>
+        <v>127.4810663600864</v>
       </c>
       <c r="E61">
-        <v>181.599</v>
+        <v>187.76</v>
       </c>
       <c r="F61">
-        <v>363.499</v>
+        <v>369.66</v>
       </c>
       <c r="G61">
         <v>30.2</v>
@@ -6649,37 +6649,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M61">
-        <v>85.71306419999999</v>
+        <v>87.165828</v>
       </c>
       <c r="N61">
-        <v>-78.91306420000001</v>
+        <v>-80.36582800000002</v>
       </c>
       <c r="O61">
-        <v>-17.360874124</v>
+        <v>-17.68048216</v>
       </c>
       <c r="P61">
-        <v>-61.552190076</v>
+        <v>-62.68534584000002</v>
       </c>
       <c r="Q61">
-        <v>-25.352190076</v>
+        <v>-26.48534584000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1298622221595155</v>
+        <v>0.1319637777135034</v>
       </c>
       <c r="T61">
-        <v>1.941390811998049</v>
+        <v>1.989925582298</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01745358206433131</v>
+        <v>0.01716268902992579</v>
       </c>
       <c r="W61">
-        <v>0.2316844453492307</v>
+        <v>0.2317530379267435</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.07933446392877863</v>
+        <v>0.0780122228632989</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6695,22 +6695,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1918373338414475</v>
+        <v>0.1937373338414475</v>
       </c>
       <c r="C62">
-        <v>-211.9789336399136</v>
+        <v>-219.777208151997</v>
       </c>
       <c r="D62">
-        <v>127.4810663600864</v>
+        <v>125.8437918480031</v>
       </c>
       <c r="E62">
-        <v>187.76</v>
+        <v>193.921</v>
       </c>
       <c r="F62">
-        <v>369.66</v>
+        <v>375.821</v>
       </c>
       <c r="G62">
         <v>30.2</v>
@@ -6731,37 +6731,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M62">
-        <v>87.165828</v>
+        <v>88.6185918</v>
       </c>
       <c r="N62">
-        <v>-80.36582800000002</v>
+        <v>-81.81859180000001</v>
       </c>
       <c r="O62">
-        <v>-17.68048216</v>
+        <v>-18.000090196</v>
       </c>
       <c r="P62">
-        <v>-62.68534584000002</v>
+        <v>-63.81850160400001</v>
       </c>
       <c r="Q62">
-        <v>-26.48534584000002</v>
+        <v>-27.618501604</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1319637777135034</v>
+        <v>0.134173105347183</v>
       </c>
       <c r="T62">
-        <v>1.989925582298</v>
+        <v>2.040949315177436</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01716268902992579</v>
+        <v>0.01688133347205815</v>
       </c>
       <c r="W62">
-        <v>0.2317530379267435</v>
+        <v>0.2318193815672887</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.0780122228632989</v>
+        <v>0.07673333396390081</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6777,22 +6777,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1937373338414475</v>
+        <v>0.1956373338414475</v>
       </c>
       <c r="C63">
-        <v>-219.777208151997</v>
+        <v>-227.5339600142412</v>
       </c>
       <c r="D63">
-        <v>125.8437918480031</v>
+        <v>124.2480399857588</v>
       </c>
       <c r="E63">
-        <v>193.921</v>
+        <v>200.082</v>
       </c>
       <c r="F63">
-        <v>375.821</v>
+        <v>381.982</v>
       </c>
       <c r="G63">
         <v>30.2</v>
@@ -6813,37 +6813,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M63">
-        <v>88.6185918</v>
+        <v>90.0713556</v>
       </c>
       <c r="N63">
-        <v>-81.81859180000001</v>
+        <v>-83.27135560000002</v>
       </c>
       <c r="O63">
-        <v>-18.000090196</v>
+        <v>-18.319698232</v>
       </c>
       <c r="P63">
-        <v>-63.81850160400001</v>
+        <v>-64.95165736800001</v>
       </c>
       <c r="Q63">
-        <v>-27.618501604</v>
+        <v>-28.75165736800001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.134173105347183</v>
+        <v>0.1364987133826352</v>
       </c>
       <c r="T63">
-        <v>2.040949315177436</v>
+        <v>2.094658507682106</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01688133347205815</v>
+        <v>0.01660905389992818</v>
       </c>
       <c r="W63">
-        <v>0.2318193815672887</v>
+        <v>0.2318835850903969</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.07673333396390081</v>
+        <v>0.07549569954512803</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6859,22 +6859,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1956373338414475</v>
+        <v>0.1975373338414475</v>
       </c>
       <c r="C64">
-        <v>-227.5339600142412</v>
+        <v>-235.250749021445</v>
       </c>
       <c r="D64">
-        <v>124.2480399857588</v>
+        <v>122.692250978555</v>
       </c>
       <c r="E64">
-        <v>200.082</v>
+        <v>206.243</v>
       </c>
       <c r="F64">
-        <v>381.982</v>
+        <v>388.143</v>
       </c>
       <c r="G64">
         <v>30.2</v>
@@ -6895,37 +6895,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M64">
-        <v>90.0713556</v>
+        <v>91.5241194</v>
       </c>
       <c r="N64">
-        <v>-83.27135560000002</v>
+        <v>-84.72411940000001</v>
       </c>
       <c r="O64">
-        <v>-18.319698232</v>
+        <v>-18.639306268</v>
       </c>
       <c r="P64">
-        <v>-64.95165736800001</v>
+        <v>-66.08481313200001</v>
       </c>
       <c r="Q64">
-        <v>-28.75165736800001</v>
+        <v>-29.884813132</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1364987133826352</v>
+        <v>0.1389500299605442</v>
       </c>
       <c r="T64">
-        <v>2.094658507682106</v>
+        <v>2.151270899781622</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01660905389992818</v>
+        <v>0.01634541812373884</v>
       </c>
       <c r="W64">
-        <v>0.2318835850903969</v>
+        <v>0.2319457504064224</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.07549569954512803</v>
+        <v>0.07429735510790392</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6941,22 +6941,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1975373338414475</v>
+        <v>0.1994373338414475</v>
       </c>
       <c r="C65">
-        <v>-235.250749021445</v>
+        <v>-242.9290578098143</v>
       </c>
       <c r="D65">
-        <v>122.692250978555</v>
+        <v>121.1749421901857</v>
       </c>
       <c r="E65">
-        <v>206.243</v>
+        <v>212.404</v>
       </c>
       <c r="F65">
-        <v>388.143</v>
+        <v>394.304</v>
       </c>
       <c r="G65">
         <v>30.2</v>
@@ -6977,37 +6977,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M65">
-        <v>91.5241194</v>
+        <v>92.97688320000002</v>
       </c>
       <c r="N65">
-        <v>-84.72411940000001</v>
+        <v>-86.17688320000002</v>
       </c>
       <c r="O65">
-        <v>-18.639306268</v>
+        <v>-18.958914304</v>
       </c>
       <c r="P65">
-        <v>-66.08481313200001</v>
+        <v>-67.21796889600002</v>
       </c>
       <c r="Q65">
-        <v>-29.884813132</v>
+        <v>-31.01796889600001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1389500299605442</v>
+        <v>0.1415375307927816</v>
       </c>
       <c r="T65">
-        <v>2.151270899781622</v>
+        <v>2.211028424775556</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01634541812373884</v>
+        <v>0.01609002096555542</v>
       </c>
       <c r="W65">
-        <v>0.2319457504064224</v>
+        <v>0.232005973056322</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.07429735510790392</v>
+        <v>0.07313645893434284</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7023,22 +7023,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1994373338414475</v>
+        <v>0.2013373338414475</v>
       </c>
       <c r="C66">
-        <v>-242.9290578098143</v>
+        <v>-250.5702965696998</v>
       </c>
       <c r="D66">
-        <v>121.1749421901857</v>
+        <v>119.6947034303002</v>
       </c>
       <c r="E66">
-        <v>212.404</v>
+        <v>218.565</v>
       </c>
       <c r="F66">
-        <v>394.304</v>
+        <v>400.465</v>
       </c>
       <c r="G66">
         <v>30.2</v>
@@ -7059,37 +7059,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M66">
-        <v>92.97688320000002</v>
+        <v>94.42964700000002</v>
       </c>
       <c r="N66">
-        <v>-86.17688320000002</v>
+        <v>-87.62964700000003</v>
       </c>
       <c r="O66">
-        <v>-18.958914304</v>
+        <v>-19.27852234000001</v>
       </c>
       <c r="P66">
-        <v>-67.21796889600002</v>
+        <v>-68.35112466000002</v>
       </c>
       <c r="Q66">
-        <v>-31.01796889600001</v>
+        <v>-32.15112466000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1415375307927816</v>
+        <v>0.1442728888154325</v>
       </c>
       <c r="T66">
-        <v>2.211028424775556</v>
+        <v>2.274200665483429</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01609002096555542</v>
+        <v>0.01584248218146995</v>
       </c>
       <c r="W66">
-        <v>0.232005973056322</v>
+        <v>0.2320643427016094</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.07313645893434284</v>
+        <v>0.07201128264304513</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7105,22 +7105,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2013373338414475</v>
+        <v>0.2032373338414475</v>
       </c>
       <c r="C67">
-        <v>-250.5702965696998</v>
+        <v>-258.1758074170863</v>
       </c>
       <c r="D67">
-        <v>119.6947034303002</v>
+        <v>118.2501925829138</v>
       </c>
       <c r="E67">
-        <v>218.565</v>
+        <v>224.726</v>
       </c>
       <c r="F67">
-        <v>400.465</v>
+        <v>406.626</v>
       </c>
       <c r="G67">
         <v>30.2</v>
@@ -7141,37 +7141,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M67">
-        <v>94.42964700000002</v>
+        <v>95.88241080000002</v>
       </c>
       <c r="N67">
-        <v>-87.62964700000003</v>
+        <v>-89.08241080000002</v>
       </c>
       <c r="O67">
-        <v>-19.27852234000001</v>
+        <v>-19.598130376</v>
       </c>
       <c r="P67">
-        <v>-68.35112466000002</v>
+        <v>-69.48428042400002</v>
       </c>
       <c r="Q67">
-        <v>-32.15112466000002</v>
+        <v>-33.28428042400002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1442728888154325</v>
+        <v>0.1471691502511805</v>
       </c>
       <c r="T67">
-        <v>2.274200665483429</v>
+        <v>2.341088920350589</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01584248218146995</v>
+        <v>0.0156024445726598</v>
       </c>
       <c r="W67">
-        <v>0.2320643427016094</v>
+        <v>0.2321209435697668</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.07201128264304513</v>
+        <v>0.07092020260299914</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7187,22 +7187,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2032373338414475</v>
+        <v>0.2051373338414474</v>
       </c>
       <c r="C68">
-        <v>-258.1758074170863</v>
+        <v>-265.7468684523179</v>
       </c>
       <c r="D68">
-        <v>118.2501925829138</v>
+        <v>116.8401315476821</v>
       </c>
       <c r="E68">
-        <v>224.726</v>
+        <v>230.887</v>
       </c>
       <c r="F68">
-        <v>406.626</v>
+        <v>412.787</v>
       </c>
       <c r="G68">
         <v>30.2</v>
@@ -7223,37 +7223,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M68">
-        <v>95.88241080000002</v>
+        <v>97.33517460000002</v>
       </c>
       <c r="N68">
-        <v>-89.08241080000002</v>
+        <v>-90.53517460000003</v>
       </c>
       <c r="O68">
-        <v>-19.598130376</v>
+        <v>-19.91773841200001</v>
       </c>
       <c r="P68">
-        <v>-69.48428042400002</v>
+        <v>-70.61743618800003</v>
       </c>
       <c r="Q68">
-        <v>-33.28428042400002</v>
+        <v>-34.41743618800002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1471691502511805</v>
+        <v>0.1502409426830345</v>
       </c>
       <c r="T68">
-        <v>2.341088920350589</v>
+        <v>2.412031008846061</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0156024445726598</v>
+        <v>0.01536957226560518</v>
       </c>
       <c r="W68">
-        <v>0.2321209435697668</v>
+        <v>0.2321758548597703</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.07092020260299914</v>
+        <v>0.06986169211638715</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7269,22 +7269,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2051373338414474</v>
+        <v>0.2070373338414475</v>
       </c>
       <c r="C69">
-        <v>-265.7468684523179</v>
+        <v>-273.2846975318591</v>
       </c>
       <c r="D69">
-        <v>116.8401315476821</v>
+        <v>115.4633024681409</v>
       </c>
       <c r="E69">
-        <v>230.887</v>
+        <v>237.048</v>
       </c>
       <c r="F69">
-        <v>412.787</v>
+        <v>418.948</v>
       </c>
       <c r="G69">
         <v>30.2</v>
@@ -7305,37 +7305,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M69">
-        <v>97.33517460000002</v>
+        <v>98.78793840000002</v>
       </c>
       <c r="N69">
-        <v>-90.53517460000003</v>
+        <v>-91.98793840000002</v>
       </c>
       <c r="O69">
-        <v>-19.91773841200001</v>
+        <v>-20.237346448</v>
       </c>
       <c r="P69">
-        <v>-70.61743618800003</v>
+        <v>-71.75059195200001</v>
       </c>
       <c r="Q69">
-        <v>-34.41743618800002</v>
+        <v>-35.550591952</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1502409426830345</v>
+        <v>0.1535047221418793</v>
       </c>
       <c r="T69">
-        <v>2.412031008846061</v>
+        <v>2.487406977872501</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01536957226560518</v>
+        <v>0.01514354914405216</v>
       </c>
       <c r="W69">
-        <v>0.2321758548597703</v>
+        <v>0.2322291511118325</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.06986169211638715</v>
+        <v>0.06883431429114628</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7351,22 +7351,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2070373338414475</v>
+        <v>0.2089373338414475</v>
       </c>
       <c r="C70">
-        <v>-273.2846975318591</v>
+        <v>-280.7904557764844</v>
       </c>
       <c r="D70">
-        <v>115.4633024681409</v>
+        <v>114.1185442235156</v>
       </c>
       <c r="E70">
-        <v>237.048</v>
+        <v>243.209</v>
       </c>
       <c r="F70">
-        <v>418.948</v>
+        <v>425.109</v>
       </c>
       <c r="G70">
         <v>30.2</v>
@@ -7387,37 +7387,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M70">
-        <v>98.78793840000002</v>
+        <v>100.2407022</v>
       </c>
       <c r="N70">
-        <v>-91.98793840000002</v>
+        <v>-93.44070220000003</v>
       </c>
       <c r="O70">
-        <v>-20.237346448</v>
+        <v>-20.55695448400001</v>
       </c>
       <c r="P70">
-        <v>-71.75059195200001</v>
+        <v>-72.88374771600003</v>
       </c>
       <c r="Q70">
-        <v>-35.550591952</v>
+        <v>-36.68374771600003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1535047221418793</v>
+        <v>0.1569790680174238</v>
       </c>
       <c r="T70">
-        <v>2.487406977872501</v>
+        <v>2.567645912642582</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01514354914405216</v>
+        <v>0.01492407741732677</v>
       </c>
       <c r="W70">
-        <v>0.2322291511118325</v>
+        <v>0.2322809025449943</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.06883431429114628</v>
+        <v>0.06783671553330339</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7433,22 +7433,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2089373338414475</v>
+        <v>0.2108373338414475</v>
       </c>
       <c r="C71">
-        <v>-280.7904557764844</v>
+        <v>-288.2652508371401</v>
       </c>
       <c r="D71">
-        <v>114.1185442235156</v>
+        <v>112.8047491628599</v>
       </c>
       <c r="E71">
-        <v>243.209</v>
+        <v>249.37</v>
       </c>
       <c r="F71">
-        <v>425.109</v>
+        <v>431.27</v>
       </c>
       <c r="G71">
         <v>30.2</v>
@@ -7469,37 +7469,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M71">
-        <v>100.2407022</v>
+        <v>101.693466</v>
       </c>
       <c r="N71">
-        <v>-93.44070220000003</v>
+        <v>-94.89346600000002</v>
       </c>
       <c r="O71">
-        <v>-20.55695448400001</v>
+        <v>-20.87656252</v>
       </c>
       <c r="P71">
-        <v>-72.88374771600003</v>
+        <v>-74.01690348000001</v>
       </c>
       <c r="Q71">
-        <v>-36.68374771600003</v>
+        <v>-37.81690348000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1569790680174238</v>
+        <v>0.1606850369513379</v>
       </c>
       <c r="T71">
-        <v>2.567645912642582</v>
+        <v>2.653234109730668</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01492407741732677</v>
+        <v>0.01471087631136495</v>
       </c>
       <c r="W71">
-        <v>0.2322809025449943</v>
+        <v>0.2323311753657802</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.06783671553330339</v>
+        <v>0.06686761959711351</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7515,22 +7515,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2108373338414475</v>
+        <v>0.2127373338414475</v>
       </c>
       <c r="C72">
-        <v>-288.2652508371401</v>
+        <v>-295.7101399377831</v>
       </c>
       <c r="D72">
-        <v>112.8047491628599</v>
+        <v>111.5208600622169</v>
       </c>
       <c r="E72">
-        <v>249.37</v>
+        <v>255.531</v>
       </c>
       <c r="F72">
-        <v>431.27</v>
+        <v>437.431</v>
       </c>
       <c r="G72">
         <v>30.2</v>
@@ -7551,37 +7551,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M72">
-        <v>101.693466</v>
+        <v>103.1462298</v>
       </c>
       <c r="N72">
-        <v>-94.89346600000002</v>
+        <v>-96.34622980000003</v>
       </c>
       <c r="O72">
-        <v>-20.87656252</v>
+        <v>-21.19617055600001</v>
       </c>
       <c r="P72">
-        <v>-74.01690348000001</v>
+        <v>-75.15005924400003</v>
       </c>
       <c r="Q72">
-        <v>-37.81690348000001</v>
+        <v>-38.95005924400003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1606850369513379</v>
+        <v>0.1646465899496599</v>
       </c>
       <c r="T72">
-        <v>2.653234109730668</v>
+        <v>2.744724941100691</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01471087631136495</v>
+        <v>0.01450368087035982</v>
       </c>
       <c r="W72">
-        <v>0.2323311753657802</v>
+        <v>0.2323800320507692</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.06686761959711351</v>
+        <v>0.06592582213799913</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7597,22 +7597,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2127373338414475</v>
+        <v>0.2146373338414475</v>
       </c>
       <c r="C73">
-        <v>-295.7101399377831</v>
+        <v>-303.1261327127649</v>
       </c>
       <c r="D73">
-        <v>111.5208600622169</v>
+        <v>110.2658672872351</v>
       </c>
       <c r="E73">
-        <v>255.531</v>
+        <v>261.692</v>
       </c>
       <c r="F73">
-        <v>437.431</v>
+        <v>443.592</v>
       </c>
       <c r="G73">
         <v>30.2</v>
@@ -7633,37 +7633,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M73">
-        <v>103.1462298</v>
+        <v>104.5989936</v>
       </c>
       <c r="N73">
-        <v>-96.3462298</v>
+        <v>-97.79899360000002</v>
       </c>
       <c r="O73">
-        <v>-21.196170556</v>
+        <v>-21.515778592</v>
       </c>
       <c r="P73">
-        <v>-75.150059244</v>
+        <v>-76.28321500800001</v>
       </c>
       <c r="Q73">
-        <v>-38.950059244</v>
+        <v>-40.08321500800001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1646465899496599</v>
+        <v>0.1688911110192906</v>
       </c>
       <c r="T73">
-        <v>2.74472494110069</v>
+        <v>2.842750831854286</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01450368087035982</v>
+        <v>0.01430224085827149</v>
       </c>
       <c r="W73">
-        <v>0.2323800320507692</v>
+        <v>0.2324275316056196</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.06592582213799925</v>
+        <v>0.06501018571941575</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7679,22 +7679,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2146373338414475</v>
+        <v>0.2165373338414475</v>
       </c>
       <c r="C74">
-        <v>-303.1261327127649</v>
+        <v>-310.5141938547662</v>
       </c>
       <c r="D74">
-        <v>110.2658672872351</v>
+        <v>109.0388061452338</v>
       </c>
       <c r="E74">
-        <v>261.692</v>
+        <v>267.853</v>
       </c>
       <c r="F74">
-        <v>443.592</v>
+        <v>449.753</v>
       </c>
       <c r="G74">
         <v>30.2</v>
@@ -7715,37 +7715,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M74">
-        <v>104.5989936</v>
+        <v>106.0517574</v>
       </c>
       <c r="N74">
-        <v>-97.79899360000002</v>
+        <v>-99.2517574</v>
       </c>
       <c r="O74">
-        <v>-21.515778592</v>
+        <v>-21.835386628</v>
       </c>
       <c r="P74">
-        <v>-76.28321500800001</v>
+        <v>-77.41637077199999</v>
       </c>
       <c r="Q74">
-        <v>-40.08321500800001</v>
+        <v>-41.21637077199999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1688911110192906</v>
+        <v>0.1734500410570421</v>
       </c>
       <c r="T74">
-        <v>2.842750831854286</v>
+        <v>2.948037899700741</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01430224085827149</v>
+        <v>0.01410631975062393</v>
       </c>
       <c r="W74">
-        <v>0.2324275316056196</v>
+        <v>0.2324737298028029</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.06501018571941575</v>
+        <v>0.06411963523010888</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7761,22 +7761,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2165373338414475</v>
+        <v>0.2184373338414475</v>
       </c>
       <c r="C75">
-        <v>-310.5141938547662</v>
+        <v>-317.8752455878763</v>
       </c>
       <c r="D75">
-        <v>109.0388061452338</v>
+        <v>107.8387544121237</v>
       </c>
       <c r="E75">
-        <v>267.853</v>
+        <v>274.014</v>
       </c>
       <c r="F75">
-        <v>449.753</v>
+        <v>455.914</v>
       </c>
       <c r="G75">
         <v>30.2</v>
@@ -7797,37 +7797,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M75">
-        <v>106.0517574</v>
+        <v>107.5045212</v>
       </c>
       <c r="N75">
-        <v>-99.2517574</v>
+        <v>-100.7045212</v>
       </c>
       <c r="O75">
-        <v>-21.835386628</v>
+        <v>-22.154994664</v>
       </c>
       <c r="P75">
-        <v>-77.41637077199999</v>
+        <v>-78.54952653600002</v>
       </c>
       <c r="Q75">
-        <v>-41.21637077199999</v>
+        <v>-42.34952653600001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1734500410570421</v>
+        <v>0.1783596580207745</v>
       </c>
       <c r="T75">
-        <v>2.948037899700741</v>
+        <v>3.061423972766154</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01410631975062393</v>
+        <v>0.01391569380804793</v>
       </c>
       <c r="W75">
-        <v>0.2324737298028029</v>
+        <v>0.2325186794000623</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.06411963523010888</v>
+        <v>0.06325315367294504</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7843,22 +7843,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2184373338414475</v>
+        <v>0.2203373338414475</v>
       </c>
       <c r="C76">
-        <v>-317.8752455878763</v>
+        <v>-325.2101699791425</v>
       </c>
       <c r="D76">
-        <v>107.8387544121237</v>
+        <v>106.6648300208575</v>
       </c>
       <c r="E76">
-        <v>274.014</v>
+        <v>280.1750000000001</v>
       </c>
       <c r="F76">
-        <v>455.914</v>
+        <v>462.075</v>
       </c>
       <c r="G76">
         <v>30.2</v>
@@ -7879,37 +7879,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M76">
-        <v>107.5045212</v>
+        <v>108.957285</v>
       </c>
       <c r="N76">
-        <v>-100.7045212</v>
+        <v>-102.157285</v>
       </c>
       <c r="O76">
-        <v>-22.154994664</v>
+        <v>-22.47460270000001</v>
       </c>
       <c r="P76">
-        <v>-78.54952653600002</v>
+        <v>-79.68268230000002</v>
       </c>
       <c r="Q76">
-        <v>-42.34952653600001</v>
+        <v>-43.48268230000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1783596580207745</v>
+        <v>0.1836620443416055</v>
       </c>
       <c r="T76">
-        <v>3.061423972766154</v>
+        <v>3.183880931676801</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01391569380804793</v>
+        <v>0.01373015122394063</v>
       </c>
       <c r="W76">
-        <v>0.2325186794000623</v>
+        <v>0.2325624303413948</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.06325315367294504</v>
+        <v>0.0624097782906391</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7925,22 +7925,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2203373338414475</v>
+        <v>0.2222373338414475</v>
       </c>
       <c r="C77">
-        <v>-325.2101699791425</v>
+        <v>-332.5198111007645</v>
       </c>
       <c r="D77">
-        <v>106.6648300208575</v>
+        <v>105.5161888992355</v>
       </c>
       <c r="E77">
-        <v>280.1750000000001</v>
+        <v>286.336</v>
       </c>
       <c r="F77">
-        <v>462.075</v>
+        <v>468.236</v>
       </c>
       <c r="G77">
         <v>30.2</v>
@@ -7961,37 +7961,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M77">
-        <v>108.957285</v>
+        <v>110.4100488</v>
       </c>
       <c r="N77">
-        <v>-102.157285</v>
+        <v>-103.6100488</v>
       </c>
       <c r="O77">
-        <v>-22.47460270000001</v>
+        <v>-22.794210736</v>
       </c>
       <c r="P77">
-        <v>-79.68268230000002</v>
+        <v>-80.81583806400002</v>
       </c>
       <c r="Q77">
-        <v>-43.48268230000002</v>
+        <v>-44.61583806400002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1836620443416055</v>
+        <v>0.1894062961891724</v>
       </c>
       <c r="T77">
-        <v>3.183880931676801</v>
+        <v>3.316542637163334</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01373015122394063</v>
+        <v>0.01354949133941509</v>
       </c>
       <c r="W77">
-        <v>0.2325624303413948</v>
+        <v>0.2326050299421659</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0624097782906391</v>
+        <v>0.06158859699734143</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8007,22 +8007,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2222373338414475</v>
+        <v>0.2241373338414475</v>
       </c>
       <c r="C78">
-        <v>-332.5198111007645</v>
+        <v>-339.804977054074</v>
       </c>
       <c r="D78">
-        <v>105.5161888992355</v>
+        <v>104.3920229459261</v>
       </c>
       <c r="E78">
-        <v>286.336</v>
+        <v>292.4970000000001</v>
       </c>
       <c r="F78">
-        <v>468.236</v>
+        <v>474.397</v>
       </c>
       <c r="G78">
         <v>30.2</v>
@@ -8043,37 +8043,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M78">
-        <v>110.4100488</v>
+        <v>111.8628126</v>
       </c>
       <c r="N78">
-        <v>-103.6100488</v>
+        <v>-105.0628126</v>
       </c>
       <c r="O78">
-        <v>-22.794210736</v>
+        <v>-23.11381877200001</v>
       </c>
       <c r="P78">
-        <v>-80.81583806400002</v>
+        <v>-81.94899382800003</v>
       </c>
       <c r="Q78">
-        <v>-44.61583806400002</v>
+        <v>-45.74899382800002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1894062961891724</v>
+        <v>0.1956500481973973</v>
       </c>
       <c r="T78">
-        <v>3.316542637163334</v>
+        <v>3.460740143126958</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01354949133941509</v>
+        <v>0.01337352391942269</v>
       </c>
       <c r="W78">
-        <v>0.2326050299421659</v>
+        <v>0.2326465230598001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.06158859699734143</v>
+        <v>0.06078874508828491</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8089,22 +8089,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2241373338414475</v>
+        <v>0.2260373338414475</v>
       </c>
       <c r="C79">
-        <v>-339.804977054074</v>
+        <v>-347.0664418654973</v>
       </c>
       <c r="D79">
-        <v>104.3920229459261</v>
+        <v>103.2915581345028</v>
       </c>
       <c r="E79">
-        <v>292.4970000000001</v>
+        <v>298.658</v>
       </c>
       <c r="F79">
-        <v>474.397</v>
+        <v>480.558</v>
       </c>
       <c r="G79">
         <v>30.2</v>
@@ -8125,37 +8125,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M79">
-        <v>111.8628126</v>
+        <v>113.3155764</v>
       </c>
       <c r="N79">
-        <v>-105.0628126</v>
+        <v>-106.5155764</v>
       </c>
       <c r="O79">
-        <v>-23.11381877200001</v>
+        <v>-23.433426808</v>
       </c>
       <c r="P79">
-        <v>-81.94899382800003</v>
+        <v>-83.08214959200001</v>
       </c>
       <c r="Q79">
-        <v>-45.74899382800002</v>
+        <v>-46.882149592</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1956500481973973</v>
+        <v>0.2024614140245517</v>
       </c>
       <c r="T79">
-        <v>3.460740143126958</v>
+        <v>3.618046513269092</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01337352391942269</v>
+        <v>0.0132020684845583</v>
       </c>
       <c r="W79">
-        <v>0.2326465230598001</v>
+        <v>0.2326869522513412</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.06078874508828491</v>
+        <v>0.06000940220253781</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8171,22 +8171,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2260373338414475</v>
+        <v>0.2279373338414475</v>
       </c>
       <c r="C80">
-        <v>-347.0664418654973</v>
+        <v>-354.304947263849</v>
       </c>
       <c r="D80">
-        <v>103.2915581345028</v>
+        <v>102.214052736151</v>
       </c>
       <c r="E80">
-        <v>298.658</v>
+        <v>304.8190000000001</v>
       </c>
       <c r="F80">
-        <v>480.558</v>
+        <v>486.7190000000001</v>
       </c>
       <c r="G80">
         <v>30.2</v>
@@ -8207,37 +8207,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M80">
-        <v>113.3155764</v>
+        <v>114.7683402</v>
       </c>
       <c r="N80">
-        <v>-106.5155764</v>
+        <v>-107.9683402</v>
       </c>
       <c r="O80">
-        <v>-23.433426808</v>
+        <v>-23.75303484400001</v>
       </c>
       <c r="P80">
-        <v>-83.08214959200001</v>
+        <v>-84.21530535600002</v>
       </c>
       <c r="Q80">
-        <v>-46.882149592</v>
+        <v>-48.01530535600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2024614140245517</v>
+        <v>0.2099214813590542</v>
       </c>
       <c r="T80">
-        <v>3.618046513269092</v>
+        <v>3.790334442472382</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0132020684845583</v>
+        <v>0.01303495369361452</v>
       </c>
       <c r="W80">
-        <v>0.2326869522513412</v>
+        <v>0.2327263579190457</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.06000940220253781</v>
+        <v>0.05924978951642956</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8253,22 +8253,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2279373338414475</v>
+        <v>0.2298373338414475</v>
       </c>
       <c r="C81">
-        <v>-354.304947263849</v>
+        <v>-361.5212043475341</v>
       </c>
       <c r="D81">
-        <v>102.214052736151</v>
+        <v>101.158795652466</v>
       </c>
       <c r="E81">
-        <v>304.8190000000001</v>
+        <v>310.98</v>
       </c>
       <c r="F81">
-        <v>486.7190000000001</v>
+        <v>492.8800000000001</v>
       </c>
       <c r="G81">
         <v>30.2</v>
@@ -8289,37 +8289,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M81">
-        <v>114.7683402</v>
+        <v>116.221104</v>
       </c>
       <c r="N81">
-        <v>-107.9683402</v>
+        <v>-109.421104</v>
       </c>
       <c r="O81">
-        <v>-23.75303484400001</v>
+        <v>-24.07264288</v>
       </c>
       <c r="P81">
-        <v>-84.21530535600002</v>
+        <v>-85.34846112000001</v>
       </c>
       <c r="Q81">
-        <v>-48.01530535600001</v>
+        <v>-49.14846112000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2099214813590542</v>
+        <v>0.2181275554270069</v>
       </c>
       <c r="T81">
-        <v>3.790334442472382</v>
+        <v>3.979851164596002</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01303495369361452</v>
+        <v>0.01287201677244434</v>
       </c>
       <c r="W81">
-        <v>0.2327263579190457</v>
+        <v>0.2327647784450576</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05924978951642956</v>
+        <v>0.05850916714747434</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8335,22 +8335,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2298373338414475</v>
+        <v>0.2317373338414475</v>
       </c>
       <c r="C82">
-        <v>-361.5212043475341</v>
+        <v>-368.7158951495307</v>
       </c>
       <c r="D82">
-        <v>101.158795652466</v>
+        <v>100.1251048504694</v>
       </c>
       <c r="E82">
-        <v>310.98</v>
+        <v>317.1410000000001</v>
       </c>
       <c r="F82">
-        <v>492.8800000000001</v>
+        <v>499.0410000000001</v>
       </c>
       <c r="G82">
         <v>30.2</v>
@@ -8371,37 +8371,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M82">
-        <v>116.221104</v>
+        <v>117.6738678</v>
       </c>
       <c r="N82">
-        <v>-109.421104</v>
+        <v>-110.8738678</v>
       </c>
       <c r="O82">
-        <v>-24.07264288</v>
+        <v>-24.39225091600001</v>
       </c>
       <c r="P82">
-        <v>-85.34846112000001</v>
+        <v>-86.48161688400002</v>
       </c>
       <c r="Q82">
-        <v>-49.14846112000001</v>
+        <v>-50.28161688400002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2181275554270069</v>
+        <v>0.2271974267652704</v>
       </c>
       <c r="T82">
-        <v>3.979851164596002</v>
+        <v>4.189317015364213</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01287201677244434</v>
+        <v>0.01271310298513021</v>
       </c>
       <c r="W82">
-        <v>0.2327647784450576</v>
+        <v>0.2328022503161063</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.05850916714747434</v>
+        <v>0.05778683175059185</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8417,22 +8417,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2317373338414475</v>
+        <v>0.2336373338414475</v>
       </c>
       <c r="C83">
-        <v>-368.7158951495307</v>
+        <v>-375.8896741073946</v>
       </c>
       <c r="D83">
-        <v>100.1251048504694</v>
+        <v>99.1123258926054</v>
       </c>
       <c r="E83">
-        <v>317.1410000000001</v>
+        <v>323.302</v>
       </c>
       <c r="F83">
-        <v>499.0410000000001</v>
+        <v>505.2020000000001</v>
       </c>
       <c r="G83">
         <v>30.2</v>
@@ -8453,37 +8453,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M83">
-        <v>117.6738678</v>
+        <v>119.1266316</v>
       </c>
       <c r="N83">
-        <v>-110.8738678</v>
+        <v>-112.3266316</v>
       </c>
       <c r="O83">
-        <v>-24.39225091600001</v>
+        <v>-24.71185895200001</v>
       </c>
       <c r="P83">
-        <v>-86.48161688400002</v>
+        <v>-87.61477264800003</v>
       </c>
       <c r="Q83">
-        <v>-50.28161688400002</v>
+        <v>-51.41477264800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2271974267652704</v>
+        <v>0.2372750615855632</v>
       </c>
       <c r="T83">
-        <v>4.189317015364213</v>
+        <v>4.422056849551113</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01271310298513021</v>
+        <v>0.01255806514384813</v>
       </c>
       <c r="W83">
-        <v>0.2328022503161063</v>
+        <v>0.2328388082390806</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05778683175059185</v>
+        <v>0.0570821142902187</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8499,22 +8499,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2336373338414475</v>
+        <v>0.2355373338414475</v>
       </c>
       <c r="C84">
-        <v>-375.8896741073946</v>
+        <v>-383.0431694449402</v>
       </c>
       <c r="D84">
-        <v>99.1123258926054</v>
+        <v>98.11983055505986</v>
       </c>
       <c r="E84">
-        <v>323.302</v>
+        <v>329.4630000000001</v>
       </c>
       <c r="F84">
-        <v>505.2020000000001</v>
+        <v>511.3630000000001</v>
       </c>
       <c r="G84">
         <v>30.2</v>
@@ -8535,37 +8535,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M84">
-        <v>119.1266316</v>
+        <v>120.5793954</v>
       </c>
       <c r="N84">
-        <v>-112.3266316</v>
+        <v>-113.7793954</v>
       </c>
       <c r="O84">
-        <v>-24.71185895200001</v>
+        <v>-25.03146698800001</v>
       </c>
       <c r="P84">
-        <v>-87.61477264800003</v>
+        <v>-88.74792841200002</v>
       </c>
       <c r="Q84">
-        <v>-51.41477264800002</v>
+        <v>-52.54792841200002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2372750615855632</v>
+        <v>0.2485383005023611</v>
       </c>
       <c r="T84">
-        <v>4.422056849551113</v>
+        <v>4.682177840701179</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01255806514384813</v>
+        <v>0.01240676315416322</v>
       </c>
       <c r="W84">
-        <v>0.2328388082390806</v>
+        <v>0.2328744852482483</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.0570821142902187</v>
+        <v>0.05639437797346925</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8581,22 +8581,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2355373338414475</v>
+        <v>0.2374373338414475</v>
       </c>
       <c r="C85">
-        <v>-383.0431694449402</v>
+        <v>-390.1769844717286</v>
       </c>
       <c r="D85">
-        <v>98.11983055505986</v>
+        <v>97.14701552827151</v>
       </c>
       <c r="E85">
-        <v>329.4630000000001</v>
+        <v>335.6240000000001</v>
       </c>
       <c r="F85">
-        <v>511.3630000000001</v>
+        <v>517.5240000000001</v>
       </c>
       <c r="G85">
         <v>30.2</v>
@@ -8617,37 +8617,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M85">
-        <v>120.5793954</v>
+        <v>122.0321592</v>
       </c>
       <c r="N85">
-        <v>-113.7793954</v>
+        <v>-115.2321592</v>
       </c>
       <c r="O85">
-        <v>-25.03146698800001</v>
+        <v>-25.35107502400001</v>
       </c>
       <c r="P85">
-        <v>-88.74792841200002</v>
+        <v>-89.88108417600003</v>
       </c>
       <c r="Q85">
-        <v>-52.54792841200002</v>
+        <v>-53.68108417600003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2485383005023611</v>
+        <v>0.2612094442837586</v>
       </c>
       <c r="T85">
-        <v>4.682177840701179</v>
+        <v>4.974813955745004</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01240676315416322</v>
+        <v>0.01225906359280413</v>
       </c>
       <c r="W85">
-        <v>0.2328744852482483</v>
+        <v>0.2329093128048168</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.05639437797346925</v>
+        <v>0.05572301633092791</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8663,22 +8663,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2374373338414475</v>
+        <v>0.2393373338414475</v>
       </c>
       <c r="C86">
-        <v>-390.1769844717284</v>
+        <v>-397.2916988060126</v>
       </c>
       <c r="D86">
-        <v>97.14701552827158</v>
+        <v>96.19330119398744</v>
       </c>
       <c r="E86">
-        <v>335.624</v>
+        <v>341.7850000000001</v>
       </c>
       <c r="F86">
-        <v>517.524</v>
+        <v>523.6850000000001</v>
       </c>
       <c r="G86">
         <v>30.2</v>
@@ -8699,37 +8699,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M86">
-        <v>122.0321592</v>
+        <v>123.484923</v>
       </c>
       <c r="N86">
-        <v>-115.2321592</v>
+        <v>-116.684923</v>
       </c>
       <c r="O86">
-        <v>-25.351075024</v>
+        <v>-25.67068306000001</v>
       </c>
       <c r="P86">
-        <v>-89.881084176</v>
+        <v>-91.01423994000002</v>
       </c>
       <c r="Q86">
-        <v>-53.681084176</v>
+        <v>-54.81423994000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2612094442837585</v>
+        <v>0.2755700739026757</v>
       </c>
       <c r="T86">
-        <v>4.974813955745</v>
+        <v>5.306468219461334</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01225906359280413</v>
+        <v>0.01211483931524173</v>
       </c>
       <c r="W86">
-        <v>0.2329093128048168</v>
+        <v>0.232943320889466</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.05572301633092791</v>
+        <v>0.05506745143291703</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8745,22 +8745,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2393373338414475</v>
+        <v>0.2412373338414475</v>
       </c>
       <c r="C87">
-        <v>-397.2916988060126</v>
+        <v>-404.3878695263461</v>
       </c>
       <c r="D87">
-        <v>96.19330119398744</v>
+        <v>95.25813047365392</v>
       </c>
       <c r="E87">
-        <v>341.7850000000001</v>
+        <v>347.946</v>
       </c>
       <c r="F87">
-        <v>523.6850000000001</v>
+        <v>529.846</v>
       </c>
       <c r="G87">
         <v>30.2</v>
@@ -8781,37 +8781,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M87">
-        <v>123.484923</v>
+        <v>124.9376868</v>
       </c>
       <c r="N87">
-        <v>-116.684923</v>
+        <v>-118.1376868</v>
       </c>
       <c r="O87">
-        <v>-25.67068306000001</v>
+        <v>-25.990291096</v>
       </c>
       <c r="P87">
-        <v>-91.01423994000002</v>
+        <v>-92.147395704</v>
       </c>
       <c r="Q87">
-        <v>-54.81423994000002</v>
+        <v>-55.947395704</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2755700739026757</v>
+        <v>0.2919822220385812</v>
       </c>
       <c r="T87">
-        <v>5.306468219461334</v>
+        <v>5.685501663708572</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01211483931524173</v>
+        <v>0.0119739690906459</v>
       </c>
       <c r="W87">
-        <v>0.232943320889466</v>
+        <v>0.2329765380884257</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.05506745143291703</v>
+        <v>0.05442713223020867</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8827,22 +8827,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2412373338414475</v>
+        <v>0.2431373338414475</v>
       </c>
       <c r="C88">
-        <v>-404.3878695263461</v>
+        <v>-411.4660322566654</v>
       </c>
       <c r="D88">
-        <v>95.25813047365392</v>
+        <v>94.34096774333463</v>
       </c>
       <c r="E88">
-        <v>347.946</v>
+        <v>354.1070000000001</v>
       </c>
       <c r="F88">
-        <v>529.846</v>
+        <v>536.0070000000001</v>
       </c>
       <c r="G88">
         <v>30.2</v>
@@ -8863,37 +8863,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M88">
-        <v>124.9376868</v>
+        <v>126.3904506</v>
       </c>
       <c r="N88">
-        <v>-118.1376868</v>
+        <v>-119.5904506</v>
       </c>
       <c r="O88">
-        <v>-25.990291096</v>
+        <v>-26.30989913200001</v>
       </c>
       <c r="P88">
-        <v>-92.147395704</v>
+        <v>-93.28055146800003</v>
       </c>
       <c r="Q88">
-        <v>-55.947395704</v>
+        <v>-57.08055146800002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2919822220385812</v>
+        <v>0.3109193160415489</v>
       </c>
       <c r="T88">
-        <v>5.685501663708572</v>
+        <v>6.122847945532309</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0119739690906459</v>
+        <v>0.01183633726201778</v>
       </c>
       <c r="W88">
-        <v>0.2329765380884257</v>
+        <v>0.2330089916736162</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.05442713223020867</v>
+        <v>0.05380153300917179</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8909,22 +8909,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2431373338414475</v>
+        <v>0.2450373338414475</v>
       </c>
       <c r="C89">
-        <v>-411.4660322566654</v>
+        <v>-418.5267021892844</v>
       </c>
       <c r="D89">
-        <v>94.34096774333463</v>
+        <v>93.4412978107156</v>
       </c>
       <c r="E89">
-        <v>354.1070000000001</v>
+        <v>360.268</v>
       </c>
       <c r="F89">
-        <v>536.0070000000001</v>
+        <v>542.168</v>
       </c>
       <c r="G89">
         <v>30.2</v>
@@ -8945,37 +8945,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M89">
-        <v>126.3904506</v>
+        <v>127.8432144</v>
       </c>
       <c r="N89">
-        <v>-119.5904506</v>
+        <v>-121.0432144</v>
       </c>
       <c r="O89">
-        <v>-26.30989913200001</v>
+        <v>-26.629507168</v>
       </c>
       <c r="P89">
-        <v>-93.28055146800003</v>
+        <v>-94.41370723200001</v>
       </c>
       <c r="Q89">
-        <v>-57.08055146800002</v>
+        <v>-58.213707232</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3109193160415489</v>
+        <v>0.3330125923783447</v>
       </c>
       <c r="T89">
-        <v>6.122847945532309</v>
+        <v>6.633085274326668</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01183633726201778</v>
+        <v>0.01170183342949485</v>
       </c>
       <c r="W89">
-        <v>0.2330089916736162</v>
+        <v>0.2330407076773251</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.05380153300917179</v>
+        <v>0.05319015195224941</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8991,22 +8991,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2450373338414475</v>
+        <v>0.2469373338414475</v>
       </c>
       <c r="C90">
-        <v>-418.5267021892844</v>
+        <v>-425.5703750499097</v>
       </c>
       <c r="D90">
-        <v>93.4412978107156</v>
+        <v>92.55862495009036</v>
       </c>
       <c r="E90">
-        <v>360.268</v>
+        <v>366.4290000000001</v>
       </c>
       <c r="F90">
-        <v>542.168</v>
+        <v>548.3290000000001</v>
       </c>
       <c r="G90">
         <v>30.2</v>
@@ -9027,37 +9027,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M90">
-        <v>127.8432144</v>
+        <v>129.2959782</v>
       </c>
       <c r="N90">
-        <v>-121.0432144</v>
+        <v>-122.4959782</v>
       </c>
       <c r="O90">
-        <v>-26.629507168</v>
+        <v>-26.94911520400001</v>
       </c>
       <c r="P90">
-        <v>-94.41370723200001</v>
+        <v>-95.54686299600002</v>
       </c>
       <c r="Q90">
-        <v>-58.213707232</v>
+        <v>-59.34686299600001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3330125923783447</v>
+        <v>0.3591228280491033</v>
       </c>
       <c r="T90">
-        <v>6.633085274326668</v>
+        <v>7.236093026538184</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01170183342949485</v>
+        <v>0.01157035215500615</v>
       </c>
       <c r="W90">
-        <v>0.2330407076773251</v>
+        <v>0.2330717109618496</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.05319015195224941</v>
+        <v>0.05259250979548247</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9073,22 +9073,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2469373338414475</v>
+        <v>0.2488373338414475</v>
       </c>
       <c r="C91">
-        <v>-425.5703750499097</v>
+        <v>-432.5975280084709</v>
       </c>
       <c r="D91">
-        <v>92.55862495009036</v>
+        <v>91.69247199152905</v>
       </c>
       <c r="E91">
-        <v>366.4290000000001</v>
+        <v>372.59</v>
       </c>
       <c r="F91">
-        <v>548.3290000000001</v>
+        <v>554.49</v>
       </c>
       <c r="G91">
         <v>30.2</v>
@@ -9109,37 +9109,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M91">
-        <v>129.2959782</v>
+        <v>130.748742</v>
       </c>
       <c r="N91">
-        <v>-122.4959782</v>
+        <v>-123.948742</v>
       </c>
       <c r="O91">
-        <v>-26.94911520400001</v>
+        <v>-27.26872324000001</v>
       </c>
       <c r="P91">
-        <v>-95.54686299600002</v>
+        <v>-96.68001876000002</v>
       </c>
       <c r="Q91">
-        <v>-59.34686299600001</v>
+        <v>-60.48001876000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3591228280491033</v>
+        <v>0.3904551108540137</v>
       </c>
       <c r="T91">
-        <v>7.236093026538184</v>
+        <v>7.959702329192003</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01157035215500615</v>
+        <v>0.01144179268661719</v>
       </c>
       <c r="W91">
-        <v>0.2330717109618496</v>
+        <v>0.2331020252844957</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.05259250979548247</v>
+        <v>0.0520081485755326</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9155,22 +9155,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2488373338414475</v>
+        <v>0.2507373338414475</v>
       </c>
       <c r="C92">
-        <v>-432.5975280084709</v>
+        <v>-439.6086205392868</v>
       </c>
       <c r="D92">
-        <v>91.69247199152905</v>
+        <v>90.8423794607133</v>
       </c>
       <c r="E92">
-        <v>372.59</v>
+        <v>378.7510000000001</v>
       </c>
       <c r="F92">
-        <v>554.49</v>
+        <v>560.6510000000001</v>
       </c>
       <c r="G92">
         <v>30.2</v>
@@ -9191,37 +9191,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M92">
-        <v>130.748742</v>
+        <v>132.2015058</v>
       </c>
       <c r="N92">
-        <v>-123.948742</v>
+        <v>-125.4015058000001</v>
       </c>
       <c r="O92">
-        <v>-27.26872324000001</v>
+        <v>-27.58833127600001</v>
       </c>
       <c r="P92">
-        <v>-96.68001876000002</v>
+        <v>-97.81317452400003</v>
       </c>
       <c r="Q92">
-        <v>-60.48001876000002</v>
+        <v>-61.61317452400003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3904551108540137</v>
+        <v>0.4287501231711263</v>
       </c>
       <c r="T92">
-        <v>7.959702329192003</v>
+        <v>8.844113699102225</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01144179268661719</v>
+        <v>0.01131605870104996</v>
       </c>
       <c r="W92">
-        <v>0.2331020252844957</v>
+        <v>0.2331316733582924</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.0520081485755326</v>
+        <v>0.05143663045931801</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9237,22 +9237,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2507373338414475</v>
+        <v>0.2526373338414475</v>
       </c>
       <c r="C93">
-        <v>-439.6086205392868</v>
+        <v>-446.6040952338196</v>
       </c>
       <c r="D93">
-        <v>90.8423794607133</v>
+        <v>90.00790476618037</v>
       </c>
       <c r="E93">
-        <v>378.7510000000001</v>
+        <v>384.912</v>
       </c>
       <c r="F93">
-        <v>560.6510000000001</v>
+        <v>566.812</v>
       </c>
       <c r="G93">
         <v>30.2</v>
@@ -9273,37 +9273,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M93">
-        <v>132.2015058</v>
+        <v>133.6542696</v>
       </c>
       <c r="N93">
-        <v>-125.4015058000001</v>
+        <v>-126.8542696</v>
       </c>
       <c r="O93">
-        <v>-27.58833127600001</v>
+        <v>-27.90793931200001</v>
       </c>
       <c r="P93">
-        <v>-97.81317452400003</v>
+        <v>-98.94633028800003</v>
       </c>
       <c r="Q93">
-        <v>-61.61317452400003</v>
+        <v>-62.74633028800002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4287501231711263</v>
+        <v>0.4766188885675173</v>
       </c>
       <c r="T93">
-        <v>8.844113699102225</v>
+        <v>9.949627911490008</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01131605870104996</v>
+        <v>0.01119305806299507</v>
       </c>
       <c r="W93">
-        <v>0.2331316733582924</v>
+        <v>0.2331606769087458</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.05143663045931801</v>
+        <v>0.05087753664997752</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9319,22 +9319,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2526373338414475</v>
+        <v>0.2545373338414475</v>
       </c>
       <c r="C94">
-        <v>-446.6040952338196</v>
+        <v>-453.5843785690454</v>
       </c>
       <c r="D94">
-        <v>90.00790476618037</v>
+        <v>89.18862143095465</v>
       </c>
       <c r="E94">
-        <v>384.912</v>
+        <v>391.0730000000001</v>
       </c>
       <c r="F94">
-        <v>566.812</v>
+        <v>572.9730000000001</v>
       </c>
       <c r="G94">
         <v>30.2</v>
@@ -9355,37 +9355,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M94">
-        <v>133.6542696</v>
+        <v>135.1070334</v>
       </c>
       <c r="N94">
-        <v>-126.8542696</v>
+        <v>-128.3070334000001</v>
       </c>
       <c r="O94">
-        <v>-27.90793931200001</v>
+        <v>-28.22754734800001</v>
       </c>
       <c r="P94">
-        <v>-98.94633028800003</v>
+        <v>-100.079486052</v>
       </c>
       <c r="Q94">
-        <v>-62.74633028800002</v>
+        <v>-63.87948605200003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4766188885675173</v>
+        <v>0.5381644440771627</v>
       </c>
       <c r="T94">
-        <v>9.949627911490008</v>
+        <v>11.37100332741715</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01119305806299507</v>
+        <v>0.01107270259995212</v>
       </c>
       <c r="W94">
-        <v>0.2331606769087458</v>
+        <v>0.2331890567269313</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.05087753664997752</v>
+        <v>0.05033046636341865</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9401,22 +9401,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2545373338414475</v>
+        <v>0.2564373338414475</v>
       </c>
       <c r="C95">
-        <v>-453.5843785690454</v>
+        <v>-460.549881634235</v>
       </c>
       <c r="D95">
-        <v>89.18862143095465</v>
+        <v>88.384118365765</v>
       </c>
       <c r="E95">
-        <v>391.0730000000001</v>
+        <v>397.234</v>
       </c>
       <c r="F95">
-        <v>572.9730000000001</v>
+        <v>579.134</v>
       </c>
       <c r="G95">
         <v>30.2</v>
@@ -9437,37 +9437,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M95">
-        <v>135.1070334</v>
+        <v>136.5597972</v>
       </c>
       <c r="N95">
-        <v>-128.3070334000001</v>
+        <v>-129.7597972</v>
       </c>
       <c r="O95">
-        <v>-28.22754734800001</v>
+        <v>-28.54715538400001</v>
       </c>
       <c r="P95">
-        <v>-100.079486052</v>
+        <v>-101.212641816</v>
       </c>
       <c r="Q95">
-        <v>-63.87948605200003</v>
+        <v>-65.01264181600003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5381644440771627</v>
+        <v>0.62022518475669</v>
       </c>
       <c r="T95">
-        <v>11.37100332741715</v>
+        <v>13.26617054865335</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01107270259995212</v>
+        <v>0.01095490789144199</v>
       </c>
       <c r="W95">
-        <v>0.2331890567269313</v>
+        <v>0.233216832719198</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05033046636341865</v>
+        <v>0.04979503587019085</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9483,22 +9483,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2564373338414475</v>
+        <v>0.2583373338414475</v>
       </c>
       <c r="C96">
-        <v>-460.549881634235</v>
+        <v>-467.5010008187555</v>
       </c>
       <c r="D96">
-        <v>88.384118365765</v>
+        <v>87.5939991812446</v>
       </c>
       <c r="E96">
-        <v>397.234</v>
+        <v>403.3950000000001</v>
       </c>
       <c r="F96">
-        <v>579.134</v>
+        <v>585.2950000000001</v>
       </c>
       <c r="G96">
         <v>30.2</v>
@@ -9519,37 +9519,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M96">
-        <v>136.5597972</v>
+        <v>138.012561</v>
       </c>
       <c r="N96">
-        <v>-129.7597972</v>
+        <v>-131.2125610000001</v>
       </c>
       <c r="O96">
-        <v>-28.54715538400001</v>
+        <v>-28.86676342000001</v>
       </c>
       <c r="P96">
-        <v>-101.212641816</v>
+        <v>-102.34579758</v>
       </c>
       <c r="Q96">
-        <v>-65.01264181600003</v>
+        <v>-66.14579758000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.62022518475669</v>
+        <v>0.7351102217080283</v>
       </c>
       <c r="T96">
-        <v>13.26617054865335</v>
+        <v>15.91940465838403</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01095490789144199</v>
+        <v>0.01083959307153207</v>
       </c>
       <c r="W96">
-        <v>0.233216832719198</v>
+        <v>0.2332440239537328</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04979503587019085</v>
+        <v>0.04927087759787296</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9565,22 +9565,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2583373338414475</v>
+        <v>0.2602373338414475</v>
       </c>
       <c r="C97">
-        <v>-467.5010008187555</v>
+        <v>-474.4381184633044</v>
       </c>
       <c r="D97">
-        <v>87.5939991812446</v>
+        <v>86.81788153669568</v>
       </c>
       <c r="E97">
-        <v>403.3950000000001</v>
+        <v>409.556</v>
       </c>
       <c r="F97">
-        <v>585.2950000000001</v>
+        <v>591.456</v>
       </c>
       <c r="G97">
         <v>30.2</v>
@@ -9601,37 +9601,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M97">
-        <v>138.012561</v>
+        <v>139.4653248</v>
       </c>
       <c r="N97">
-        <v>-131.2125610000001</v>
+        <v>-132.6653248</v>
       </c>
       <c r="O97">
-        <v>-28.86676342000001</v>
+        <v>-29.18637145600001</v>
       </c>
       <c r="P97">
-        <v>-102.34579758</v>
+        <v>-103.478953344</v>
       </c>
       <c r="Q97">
-        <v>-66.14579758000004</v>
+        <v>-67.27895334400003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7351102217080283</v>
+        <v>0.9074377771350357</v>
       </c>
       <c r="T97">
-        <v>15.91940465838403</v>
+        <v>19.89925582298004</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01083959307153207</v>
+        <v>0.01072668064370361</v>
       </c>
       <c r="W97">
-        <v>0.2332440239537328</v>
+        <v>0.2332706487042147</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04927087759787296</v>
+        <v>0.04875763928956178</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9647,22 +9647,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2602373338414475</v>
+        <v>0.2621373338414474</v>
       </c>
       <c r="C98">
-        <v>-474.4381184633044</v>
+        <v>-481.3616034768277</v>
       </c>
       <c r="D98">
-        <v>86.81788153669568</v>
+        <v>86.05539652317231</v>
       </c>
       <c r="E98">
-        <v>409.556</v>
+        <v>415.717</v>
       </c>
       <c r="F98">
-        <v>591.456</v>
+        <v>597.617</v>
       </c>
       <c r="G98">
         <v>30.2</v>
@@ -9683,37 +9683,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M98">
-        <v>139.4653248</v>
+        <v>140.9180886</v>
       </c>
       <c r="N98">
-        <v>-132.6653248</v>
+        <v>-134.1180886</v>
       </c>
       <c r="O98">
-        <v>-29.18637145600001</v>
+        <v>-29.50597949200001</v>
       </c>
       <c r="P98">
-        <v>-103.478953344</v>
+        <v>-104.612109108</v>
       </c>
       <c r="Q98">
-        <v>-67.27895334400003</v>
+        <v>-68.41210910800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9074377771350333</v>
+        <v>1.194650369513378</v>
       </c>
       <c r="T98">
-        <v>19.89925582297998</v>
+        <v>26.53234109730665</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01072668064370361</v>
+        <v>0.01061609630717059</v>
       </c>
       <c r="W98">
-        <v>0.2332706487042147</v>
+        <v>0.2332967244907692</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04875763928956178</v>
+        <v>0.04825498321441168</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9729,22 +9729,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2621373338414474</v>
+        <v>0.2640373338414475</v>
       </c>
       <c r="C99">
-        <v>-481.3616034768277</v>
+        <v>-488.2718119212125</v>
       </c>
       <c r="D99">
-        <v>86.05539652317231</v>
+        <v>85.3061880787875</v>
       </c>
       <c r="E99">
-        <v>415.717</v>
+        <v>421.878</v>
       </c>
       <c r="F99">
-        <v>597.617</v>
+        <v>603.778</v>
       </c>
       <c r="G99">
         <v>30.2</v>
@@ -9765,37 +9765,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M99">
-        <v>140.9180886</v>
+        <v>142.3708524</v>
       </c>
       <c r="N99">
-        <v>-134.1180886</v>
+        <v>-135.5708524</v>
       </c>
       <c r="O99">
-        <v>-29.50597949200001</v>
+        <v>-29.82558752800001</v>
       </c>
       <c r="P99">
-        <v>-104.612109108</v>
+        <v>-105.745264872</v>
       </c>
       <c r="Q99">
-        <v>-68.41210910800001</v>
+        <v>-69.54526487200003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.194650369513378</v>
+        <v>1.769075554270067</v>
       </c>
       <c r="T99">
-        <v>26.53234109730665</v>
+        <v>39.79851164595997</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01061609630717059</v>
+        <v>0.01050776879383211</v>
       </c>
       <c r="W99">
-        <v>0.2332967244907692</v>
+        <v>0.2333222681184144</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04825498321441168</v>
+        <v>0.04776258542650957</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9811,22 +9811,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2640373338414475</v>
+        <v>0.2659373338414475</v>
       </c>
       <c r="C100">
-        <v>-488.2718119212125</v>
+        <v>-495.1690875656991</v>
       </c>
       <c r="D100">
-        <v>85.3061880787875</v>
+        <v>84.56991243430083</v>
       </c>
       <c r="E100">
-        <v>421.878</v>
+        <v>428.039</v>
       </c>
       <c r="F100">
-        <v>603.778</v>
+        <v>609.939</v>
       </c>
       <c r="G100">
         <v>30.2</v>
@@ -9847,37 +9847,37 @@
         <v>6.79999999999999</v>
       </c>
       <c r="M100">
-        <v>142.3708524</v>
+        <v>143.8236162</v>
       </c>
       <c r="N100">
-        <v>-135.5708524</v>
+        <v>-137.0236162</v>
       </c>
       <c r="O100">
-        <v>-29.82558752800001</v>
+        <v>-30.14519556400001</v>
       </c>
       <c r="P100">
-        <v>-105.745264872</v>
+        <v>-106.878420636</v>
       </c>
       <c r="Q100">
-        <v>-69.54526487200003</v>
+        <v>-70.67842063600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.769075554270067</v>
+        <v>3.492351108540133</v>
       </c>
       <c r="T100">
-        <v>39.79851164595997</v>
+        <v>79.59702329191994</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01050776879383211</v>
+        <v>0.01040162971510654</v>
       </c>
       <c r="W100">
-        <v>0.2333222681184144</v>
+        <v>0.2333472957131779</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9885,91 +9885,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04776258542650957</v>
+        <v>0.04728013506866602</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2659373338414475</v>
-      </c>
-      <c r="C101">
-        <v>-495.1690875656991</v>
-      </c>
-      <c r="D101">
-        <v>84.56991243430083</v>
-      </c>
-      <c r="E101">
-        <v>428.039</v>
-      </c>
-      <c r="F101">
-        <v>609.939</v>
-      </c>
-      <c r="G101">
-        <v>30.2</v>
-      </c>
-      <c r="H101">
-        <v>434.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>42.99999999999999</v>
-      </c>
-      <c r="K101">
-        <v>36.2</v>
-      </c>
-      <c r="L101">
-        <v>6.79999999999999</v>
-      </c>
-      <c r="M101">
-        <v>143.8236162</v>
-      </c>
-      <c r="N101">
-        <v>-137.0236162</v>
-      </c>
-      <c r="O101">
-        <v>-30.14519556400001</v>
-      </c>
-      <c r="P101">
-        <v>-106.878420636</v>
-      </c>
-      <c r="Q101">
-        <v>-70.67842063600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.492351108540133</v>
-      </c>
-      <c r="T101">
-        <v>79.59702329191994</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01040162971510654</v>
-      </c>
-      <c r="W101">
-        <v>0.2333472957131779</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04728013506866602</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
